--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,301 +656,313 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3517000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3641000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3661000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3738000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3800000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4390000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4612000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4676000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4847000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4887000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4924000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5029000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5125000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5167000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5192000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5228000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5306000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5350000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5375000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5427000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1737000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1850000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1740000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1817000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1826000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1999000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2058000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1985000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2086000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2151000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2115000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2136000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2231000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2236000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2232000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2235000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2257000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2334000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2243000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2300000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1780000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1921000</v>
       </c>
       <c r="F10" s="3">
         <v>1921000</v>
       </c>
       <c r="G10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="H10" s="3">
         <v>1974000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2391000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2554000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2691000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2761000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2736000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2809000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2893000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2894000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2931000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2960000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2993000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3049000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3016000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3132000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3127000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +986,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1052,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,32 +1120,35 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1873000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-42000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8760000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-581000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3504000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-639000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1140,23 +1159,23 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-8000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2665000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>79000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1164,78 +1183,84 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>6506000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>751000</v>
+      </c>
+      <c r="E15" s="3">
         <v>755000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>746000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>733000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>796000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>808000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>827000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>808000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>877000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>951000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1041000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1150000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1195000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1193000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1162000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1160000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1210000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1235000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1196000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1188000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5257000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3354000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12036000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2690000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6797000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2960000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3700000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3593000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3686000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3756000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3918000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4034000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6957000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4275000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4296000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4327000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4459000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4400000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4399000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10926000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1740000</v>
+      </c>
+      <c r="E18" s="3">
         <v>287000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8375000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1048000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1430000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>912000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1083000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1161000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1131000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1006000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>995000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>892000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>896000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>901000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>847000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>950000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>976000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,333 +1443,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-77000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-21000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-89000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>95000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-130000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-122000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>70000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-110000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-38000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>52000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>26000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>31000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-44000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>44000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1101000</v>
+      </c>
+      <c r="E21" s="3">
         <v>965000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7650000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1692000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2108000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1617000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1961000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1928000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2044000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2099000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2171000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-617000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2082000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2089000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2042000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2046000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2141000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2216000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E22" s="3">
         <v>295000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>294000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>279000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>280000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>363000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>337000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>352000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>372000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>377000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>384000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>389000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>396000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>409000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>414000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>449000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>487000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>496000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>518000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>523000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2142000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-85000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>680000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>937000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>453000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>801000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>679000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>716000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>674000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>632000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>480000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>513000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>433000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>349000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>410000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>502000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>46000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>169000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-113000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>359000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>109000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>202000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>171000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>172000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>168000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>157000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>81000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>114000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>136000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>119000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>126000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>108000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>131000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>138000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1995000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-78000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>511000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>578000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>344000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>599000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>508000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>544000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>506000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>475000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>366000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>377000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>314000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>223000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>302000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>371000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1995000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-78000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>511000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>578000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>344000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>599000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>508000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>544000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>506000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>475000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>366000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>377000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>314000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>223000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>302000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>371000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2040,8 +2100,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2058,11 +2118,14 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2257,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E32" s="3">
         <v>77000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>21000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>89000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-95000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>130000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>122000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-70000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>110000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>38000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-52000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-26000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-31000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>44000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-44000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1995000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-78000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>511000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>578000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>344000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>599000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>508000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>544000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>506000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>475000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>366000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>377000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>314000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>223000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>302000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>371000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1995000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-78000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>511000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>578000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>344000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>599000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>508000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>544000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>506000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>475000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>366000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>377000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>314000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>223000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>302000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>371000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2656,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2234000</v>
+      </c>
+      <c r="E41" s="3">
         <v>311000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>411000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1148000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1251000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>252000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>360000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>366000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>354000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>635000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>935000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>486000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>406000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>526000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1763000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1564000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1690000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1404000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>410000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>441000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,268 +2790,283 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1553000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1581000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1450000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1497000</v>
-      </c>
       <c r="H43" s="3">
+        <v>1528000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1552000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1529000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1586000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1723000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1605000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1970000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1953000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2035000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2184000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2284000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2281000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2336000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2346000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2590000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2474000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E44" s="3">
         <v>227000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>205000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>223000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>236000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>179000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>151000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>128000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>96000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>103000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>114000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>100000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>105000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>112000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>122000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>119000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>105000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>137000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>151000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>154000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2555000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2676000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2584000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2436000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7399000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9750000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9692000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9363000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9358000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>727000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>754000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>630000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>682000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>689000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>726000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>637000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>702000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>727000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>751000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4775000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4646000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4873000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5405000</v>
       </c>
-      <c r="G46" s="3">
-        <v>5420000</v>
-      </c>
       <c r="H46" s="3">
+        <v>5451000</v>
+      </c>
+      <c r="I46" s="3">
         <v>9382000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11790000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11772000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11536000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11701000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3746000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3293000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3176000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3504000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4858000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4690000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4768000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4589000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="V46" s="3">
-        <v>3820000</v>
       </c>
       <c r="W46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3026,138 +3130,147 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20988000</v>
+      </c>
+      <c r="E48" s="3">
         <v>19606000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19432000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19321000</v>
       </c>
-      <c r="G48" s="3">
-        <v>19166000</v>
-      </c>
       <c r="H48" s="3">
+        <v>20506000</v>
+      </c>
+      <c r="I48" s="3">
         <v>20713000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20720000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20829000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22346000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20926000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25993000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26091000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28037000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26290000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26079000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27623000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27765000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27595000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27704000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27745000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7434000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9608000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9763000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18691000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18823000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22354000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22575000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22761000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22956000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23147000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26530000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26738000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27089000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30039000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>30372000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>30699000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>31101000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>31386000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>31734000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>32035000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3402,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>821000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2061000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2100000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2113000</v>
       </c>
-      <c r="G52" s="3">
-        <v>2172000</v>
-      </c>
       <c r="H52" s="3">
+        <v>832000</v>
+      </c>
+      <c r="I52" s="3">
         <v>2368000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2590000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2675000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1155000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2534000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2678000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2706000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1092000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2766000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2862000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1044000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1108000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1158000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1192000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1188000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3538,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34018000</v>
+      </c>
+      <c r="E54" s="3">
         <v>35921000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36168000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45530000</v>
       </c>
-      <c r="G54" s="3">
-        <v>45581000</v>
-      </c>
       <c r="H54" s="3">
+        <v>45612000</v>
+      </c>
+      <c r="I54" s="3">
         <v>54817000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>57675000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>58037000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57993000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>58308000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58947000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58828000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>59394000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62599000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>64171000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>64056000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64742000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64728000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64508000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64788000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,398 +3660,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1015000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1171000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1131000</v>
       </c>
-      <c r="G57" s="3">
-        <v>950000</v>
-      </c>
       <c r="H57" s="3">
+        <v>1044000</v>
+      </c>
+      <c r="I57" s="3">
         <v>1009000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1053000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>902000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>758000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>829000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>966000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1017000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1134000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1364000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1448000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1581000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1724000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1712000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1634000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1481000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E58" s="3">
         <v>155000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>154000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>153000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>154000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>156000</v>
       </c>
       <c r="J58" s="3">
         <v>156000</v>
       </c>
       <c r="K58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="L58" s="3">
         <v>1554000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2501000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2595000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3841000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2427000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1487000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2885000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1129000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2300000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1744000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1595000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>632000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2243000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2750000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2638000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3564000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3699000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4232000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4572000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4597000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4857000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4970000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2949000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2929000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3073000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3028000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3139000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2993000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3234000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3133000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3266000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3260000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3534000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3920000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3963000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4848000</v>
       </c>
-      <c r="G60" s="3">
-        <v>4803000</v>
-      </c>
       <c r="H60" s="3">
+        <v>4897000</v>
+      </c>
+      <c r="I60" s="3">
         <v>8715000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5781000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5655000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7169000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8300000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6510000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7787000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6634000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5879000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7472000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5703000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7258000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6589000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6495000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5373000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19831000</v>
+      </c>
+      <c r="E61" s="3">
         <v>19740000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19899000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19743000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20418000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21764000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27965000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28397000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27428000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27260000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28574000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27599000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29410000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31105000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31414000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33481000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32394000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33381000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33193000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>34858000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10236000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10042000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10022000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9944000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9923000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11761000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11710000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11703000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11556000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11565000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12157000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12139000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12188000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11926000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11823000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11581000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11620000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11084000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11128000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11014000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4270,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33601000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33702000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33884000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34535000</v>
       </c>
-      <c r="G66" s="3">
-        <v>35144000</v>
-      </c>
       <c r="H66" s="3">
+        <v>35238000</v>
+      </c>
+      <c r="I66" s="3">
         <v>42240000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45456000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45755000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46153000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>47125000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47241000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47525000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48232000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48910000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50709000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50765000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51272000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51054000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50816000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51245000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4636,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17907000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="G72" s="3">
-        <v>-7546000</v>
-      </c>
       <c r="H72" s="3">
+        <v>-7609000</v>
+      </c>
+      <c r="I72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4908,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2219000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2284000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10995000</v>
       </c>
-      <c r="G76" s="3">
-        <v>10437000</v>
-      </c>
       <c r="H76" s="3">
+        <v>10374000</v>
+      </c>
+      <c r="I76" s="3">
         <v>12577000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12219000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12282000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11840000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11183000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11706000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11303000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11162000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13689000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13462000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13291000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13470000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13674000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13692000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13543000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1995000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-78000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>511000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>578000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>344000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>599000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>508000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>544000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>506000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>475000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>366000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>377000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>314000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>223000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>302000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>371000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5213,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>751000</v>
+      </c>
+      <c r="E83" s="3">
         <v>755000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>746000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>733000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>796000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>808000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>827000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>808000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>877000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>951000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1041000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1150000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1195000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1193000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1162000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1160000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1210000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1235000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1196000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1188000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E89" s="3">
         <v>881000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>595000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>841000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1123000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1396000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1375000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1607000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1730000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1639000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1525000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1682000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1794000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1749000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1299000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1909000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1888000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1701000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1182000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5715,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-821000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-843000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-796000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-640000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-833000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-845000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-761000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-577000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-848000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-690000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-646000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-716000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-758000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-988000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-974000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-940000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-957000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-931000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5917,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1031000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-827000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-789000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-616000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4882000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1864000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-701000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-569000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-763000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-654000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-620000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-675000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-724000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-942000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-959000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-939000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-899000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-954000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-811000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-906000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5793,61 +6026,64 @@
         <v>-1000</v>
       </c>
       <c r="F96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-8000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-255000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-254000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-271000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-253000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-266000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-274000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-294000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-272000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-275000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-271000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-291000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-271000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-275000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-269000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-285000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6283,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-173000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>158000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-86000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-713000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-776000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-576000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-774000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-597000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-486000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-724000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>57000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-924000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-320000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1898000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-119000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-731000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-107000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1042000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-156000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-295000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-242000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>443000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>76000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-120000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>193000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-126000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>286000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>991000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-34000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-44000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,313 +656,325 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3290000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3517000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3641000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3661000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3738000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3800000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4390000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4612000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4676000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4847000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4887000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4924000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5029000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5125000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5167000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5192000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5228000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5306000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5350000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5375000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5427000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1652000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1737000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1850000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1740000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1817000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1826000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1999000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2058000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1985000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2086000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2151000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2115000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2136000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2231000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2236000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2232000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2235000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2257000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2334000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2243000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2300000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1780000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1921000</v>
       </c>
       <c r="G10" s="3">
         <v>1921000</v>
       </c>
       <c r="H10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1974000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2391000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2554000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2691000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2761000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2736000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2809000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2893000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2894000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2931000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2960000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2993000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3049000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3016000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3132000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3127000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +999,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,35 +1139,38 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1873000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-42000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8760000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-581000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3504000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-639000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1162,23 +1181,23 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-8000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2665000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-4000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>79000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1186,81 +1205,87 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>6506000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>748000</v>
+      </c>
+      <c r="E15" s="3">
         <v>751000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>755000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>746000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>733000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>796000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>808000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>827000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>808000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>877000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>951000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1041000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1150000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1195000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1193000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1162000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1160000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1210000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1235000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1196000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1188000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2935000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5257000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3354000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12036000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2690000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6797000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2960000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3700000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3593000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3686000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3756000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3918000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4034000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6957000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4275000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4296000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4327000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4459000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4400000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4399000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10926000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1740000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>287000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8375000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1048000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1430000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>912000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1083000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1161000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1131000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1006000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>995000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>892000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>896000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>901000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>847000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>950000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>976000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,348 +1476,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-112000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-77000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-21000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-89000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>95000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-130000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-122000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>70000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-110000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-38000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>52000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>26000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>31000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-19000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-44000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>44000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1141000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1101000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>965000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7650000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1692000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2108000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1617000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1961000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1928000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2044000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2099000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2171000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-617000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2082000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2089000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2042000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2046000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2141000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2216000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E22" s="3">
         <v>290000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>295000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>294000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>279000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>280000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>363000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>337000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>352000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>372000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>377000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>384000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>389000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>396000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>409000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>414000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>449000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>487000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>496000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>518000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>523000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-85000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>680000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>937000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>453000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>801000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>679000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>716000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>674000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>632000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>480000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>513000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>433000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>349000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>410000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>502000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-147000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>46000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>169000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-113000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>359000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>109000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>202000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>171000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>172000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>168000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>157000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>81000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>114000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>136000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>119000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>126000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>108000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>131000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>138000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-78000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>511000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>578000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>344000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>599000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>508000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>544000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>506000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>475000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>366000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>377000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>314000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>223000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>302000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>371000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-78000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>511000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>578000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>344000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>599000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>508000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>544000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>506000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>475000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>366000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>377000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>314000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>223000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>302000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>371000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2103,8 +2163,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2121,11 +2181,14 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,144 +2326,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E32" s="3">
         <v>112000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>77000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>21000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>89000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-95000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>130000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>122000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-70000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>110000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>38000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-52000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-26000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-31000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>19000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>44000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-44000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-78000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>511000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>578000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>344000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>599000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>508000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>544000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>506000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>475000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>366000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>377000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>314000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>223000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>302000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>371000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-78000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>511000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>578000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>344000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>599000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>508000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>544000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>506000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>475000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>366000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>377000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>314000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>223000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>302000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>371000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,76 +2742,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2234000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>311000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>411000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1148000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1251000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>252000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>360000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>366000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>354000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>635000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>935000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>486000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>406000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>526000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1763000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1564000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1690000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1404000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>410000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>441000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,280 +2882,295 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1351000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1610000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1553000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1581000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1450000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1528000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1552000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1529000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1586000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1723000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1605000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1970000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1953000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2035000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2184000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2284000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2281000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2336000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2346000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2590000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2474000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E44" s="3">
         <v>209000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>227000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>205000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>223000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>236000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>179000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>151000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>128000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>96000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>103000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>114000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>100000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>105000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>112000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>122000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>119000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>105000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>137000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>151000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>154000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>811000</v>
+      </c>
+      <c r="E45" s="3">
         <v>722000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2555000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2676000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2584000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2436000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7399000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9750000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9692000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9363000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9358000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>727000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>754000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>630000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>682000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>689000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>726000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>637000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>702000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>727000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>751000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3935000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4775000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4646000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4873000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5405000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5451000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9382000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11790000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11772000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11536000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11701000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3746000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3293000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3176000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3504000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4858000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4690000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4768000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4589000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="W46" s="3">
-        <v>3820000</v>
       </c>
       <c r="X46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3133,144 +3237,153 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19908000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20988000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19606000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19432000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19321000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20506000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20713000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20720000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20829000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22346000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20926000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25993000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26091000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>28037000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26290000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26079000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27623000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27765000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27595000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27704000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27745000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7254000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7434000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9608000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9763000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18691000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18823000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22354000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22575000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22761000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22956000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23147000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26530000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26738000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27089000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>30039000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>30372000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>30699000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>31101000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>31386000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>31734000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>32035000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,76 +3521,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2076000</v>
+      </c>
+      <c r="E52" s="3">
         <v>821000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2061000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2100000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2113000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>832000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2368000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2590000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2675000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1155000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2534000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2678000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2706000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1092000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2766000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2862000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1044000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1108000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1158000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1192000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1188000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,76 +3663,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33173000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34018000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>35921000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36168000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45530000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45612000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54817000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>57675000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>58037000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57993000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58308000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58947000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58828000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59394000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62599000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>64171000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64056000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64742000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64728000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64508000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64788000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,416 +3790,435 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1162000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1134000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1015000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1171000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1131000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1044000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1009000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1053000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>902000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>758000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>829000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>966000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1017000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1134000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1364000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1448000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1581000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1724000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1712000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1634000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1481000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E58" s="3">
         <v>157000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>155000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>154000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>153000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>154000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>156000</v>
       </c>
       <c r="K58" s="3">
         <v>156000</v>
       </c>
       <c r="L58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="M58" s="3">
         <v>1554000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2501000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2595000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3841000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2427000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1487000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2885000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1129000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2300000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1744000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1595000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>632000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2568000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2243000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2750000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2638000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3564000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3699000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4232000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4572000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4597000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4857000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4970000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2949000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2929000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3073000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3028000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3139000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2993000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3234000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3133000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3266000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3260000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3816000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3534000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3920000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3963000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4848000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4897000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8715000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5781000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5655000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7169000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8300000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6510000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7787000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6634000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5879000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7472000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5703000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7258000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6589000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6495000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5373000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18591000</v>
+      </c>
+      <c r="E61" s="3">
         <v>19831000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19740000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19899000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19743000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20418000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21764000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27965000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28397000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27428000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27260000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28574000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27599000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29410000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31105000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31414000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>33481000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32394000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33381000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33193000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>34858000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10262000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10236000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10042000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10022000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9944000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9923000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11761000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11710000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11703000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11556000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11565000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12157000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12139000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12188000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11926000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11823000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11581000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11620000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11084000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11128000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11014000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,76 +4427,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32669000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33601000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33702000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33884000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34535000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35238000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42240000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45456000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45755000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46153000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47125000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47241000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47525000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48232000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48910000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50709000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>50765000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51272000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51054000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50816000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51245000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,76 +4809,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17850000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,76 +5093,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E76" s="3">
         <v>417000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2219000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2284000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10995000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10374000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12577000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12219000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12282000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11840000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11183000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11706000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11303000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11162000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13689000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13462000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13291000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13470000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13674000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13692000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13543000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-78000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>511000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>578000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>344000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>599000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>508000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>544000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>506000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>475000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>366000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>377000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>314000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>223000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>302000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>371000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,76 +5411,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>748000</v>
+      </c>
+      <c r="E83" s="3">
         <v>751000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>755000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>746000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>733000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>796000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>808000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>827000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>808000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>877000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>951000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1041000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1150000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1195000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1193000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1162000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1160000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1210000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1235000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1196000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1188000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5835,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1102000</v>
+      </c>
+      <c r="E89" s="3">
         <v>784000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>881000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>595000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>841000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1123000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1396000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1375000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1607000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1730000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1639000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1525000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1682000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1794000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1749000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1299000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1909000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1888000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1701000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1182000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,76 +5935,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-713000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-821000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-843000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-796000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-640000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-833000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-845000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-761000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-577000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-848000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-690000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-646000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-716000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-758000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-988000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-974000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-940000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-957000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-931000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6146,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-698000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1031000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-827000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-789000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-616000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4882000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1864000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-701000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-569000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-763000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-654000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-620000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-675000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-724000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-942000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-959000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-939000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-899000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-954000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-811000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-906000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,13 +6246,14 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1000</v>
+        <v>-3000</v>
       </c>
       <c r="E96" s="3">
         <v>-1000</v>
@@ -6029,61 +6262,64 @@
         <v>-1000</v>
       </c>
       <c r="G96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-8000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-255000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-254000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-271000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-253000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-266000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-274000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-294000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-272000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-275000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-271000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-291000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-271000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-275000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-269000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-285000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,76 +6528,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1060000</v>
+      </c>
+      <c r="E100" s="3">
         <v>83000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-173000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>158000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-86000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-713000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-776000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-576000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-774000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-597000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-486000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-724000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>57000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-924000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-320000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6422,72 +6670,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-656000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1898000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-119000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-731000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-107000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1042000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-156000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-295000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-242000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>443000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>76000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>193000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-126000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>286000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>991000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-34000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-44000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,325 +656,337 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3268000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3290000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3517000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3641000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3661000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3738000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3800000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4390000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4612000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4676000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4847000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4887000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4924000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5029000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5125000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5167000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5192000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5228000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5306000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5350000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5375000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5427000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1653000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1652000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1737000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1850000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1740000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1817000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1826000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1999000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2058000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1985000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2086000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2151000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2115000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2136000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2231000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2236000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2232000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2235000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2257000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2334000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2243000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1615000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1638000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1780000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1921000</v>
       </c>
       <c r="H10" s="3">
         <v>1921000</v>
       </c>
       <c r="I10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1974000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2391000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2554000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2691000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2761000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2736000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2809000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2893000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2894000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2931000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2960000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2993000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3049000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3016000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3132000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3127000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,8 +1012,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,38 +1158,41 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-288000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1873000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-42000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8760000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-581000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3504000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-639000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1184,23 +1203,23 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2665000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-4000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>79000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1208,84 +1227,90 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>6506000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>743000</v>
+      </c>
+      <c r="E15" s="3">
         <v>748000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>751000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>755000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>746000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>733000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>796000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>808000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>827000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>808000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>877000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>951000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1041000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1150000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1195000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1193000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1162000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1160000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1210000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1235000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1196000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1188000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1333,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3095000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2935000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5257000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3354000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12036000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2690000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6797000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2960000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3700000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3593000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3686000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3756000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3918000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4034000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6957000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4275000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4296000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4327000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4459000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4400000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4399000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10926000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E18" s="3">
         <v>355000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1740000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>287000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8375000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1048000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1430000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>912000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1083000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1161000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1131000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1006000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>995000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>892000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>896000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>901000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>847000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>950000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>976000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,363 +1509,379 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E20" s="3">
         <v>38000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-112000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-77000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-21000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-89000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>95000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-130000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-122000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>70000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-110000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-38000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>52000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>26000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>20000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>31000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-44000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>44000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1075000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1141000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1101000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>965000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7650000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1692000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2108000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1617000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1961000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1928000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2044000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2099000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2171000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-617000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2082000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2089000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2042000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2046000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2141000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2216000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E22" s="3">
         <v>291000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>290000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>295000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>294000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>279000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>280000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>363000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>337000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>352000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>372000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>377000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>384000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>389000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>396000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>409000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>414000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>449000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>487000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>496000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>518000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>523000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E23" s="3">
         <v>102000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-85000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>680000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>937000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>453000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>801000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>679000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>716000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>674000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>632000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>480000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>513000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>433000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>349000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>410000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>502000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E24" s="3">
         <v>45000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-147000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>46000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>169000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-113000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>359000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>109000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>202000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>171000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>172000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>168000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>157000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>81000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>114000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>136000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>119000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>126000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>108000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>131000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>138000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1951,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E26" s="3">
         <v>57000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-78000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>511000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>578000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>344000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>599000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>508000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>544000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>506000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>475000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>366000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>377000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>314000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>223000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>302000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>371000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E27" s="3">
         <v>57000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-78000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>511000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>578000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>344000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>599000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>508000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>544000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>506000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>475000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>366000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>377000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>314000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>223000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>302000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>371000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2166,8 +2226,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2184,11 +2244,14 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,150 +2395,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-159000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-38000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>112000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>77000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>21000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>89000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-95000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>130000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>122000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-70000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>110000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>38000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-52000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-20000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-31000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>44000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-44000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E33" s="3">
         <v>57000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-78000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>511000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>578000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>344000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>599000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>508000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>544000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>506000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>475000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>366000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>377000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>314000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>223000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>302000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>371000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2617,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E35" s="3">
         <v>57000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-78000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>511000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>578000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>344000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>599000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>508000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>544000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>506000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>475000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>366000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>377000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>314000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>223000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>302000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>371000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,79 +2828,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1495000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1580000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2234000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>311000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>411000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1148000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1251000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>252000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>360000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>366000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>354000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>635000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>935000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>486000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>406000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>526000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1763000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1564000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1690000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1404000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>410000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>441000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2885,292 +2974,307 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1351000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1610000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1553000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1581000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1450000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1528000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1552000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1529000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1586000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1723000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1605000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1970000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1953000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2035000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2184000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2284000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2281000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2336000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2346000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2590000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2474000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E44" s="3">
         <v>193000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>209000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>227000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>205000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>223000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>236000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>179000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>151000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>128000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>96000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>103000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>114000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>100000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>105000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>112000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>122000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>119000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>105000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>137000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>151000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>154000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>751000</v>
+      </c>
+      <c r="E45" s="3">
         <v>811000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>722000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2555000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2676000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2584000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2436000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7399000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9750000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9692000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9363000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9358000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>727000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>754000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>630000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>682000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>689000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>726000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>637000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>702000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>727000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>751000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3760000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3935000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4775000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4646000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4873000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5405000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5451000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9382000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11790000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11772000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11536000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11701000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3746000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3293000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3176000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3504000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4858000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4690000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4768000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4589000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="X46" s="3">
-        <v>3820000</v>
       </c>
       <c r="Y46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3240,150 +3344,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20089000</v>
+      </c>
+      <c r="E48" s="3">
         <v>19908000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20988000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19606000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19432000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19321000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20506000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20713000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20720000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20829000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22346000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20926000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25993000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26091000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>28037000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26290000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26079000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27623000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27765000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27595000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27704000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27745000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7091000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7254000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7434000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9608000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9763000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18691000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18823000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22354000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22575000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22761000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22956000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23147000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26530000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26738000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>27089000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>30039000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>30372000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>30699000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>31101000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>31386000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>31734000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>32035000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,79 +3640,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2003000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2076000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>821000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2061000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2113000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>832000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2368000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2590000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2675000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1155000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2534000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2678000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2706000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1092000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2766000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2862000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1044000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1108000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1158000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1192000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1188000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,79 +3788,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32943000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33173000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34018000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35921000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36168000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45530000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45612000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>54817000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57675000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>58037000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57993000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58308000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58947000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58828000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>59394000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>62599000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64171000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64056000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64742000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64728000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64508000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64788000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,434 +3920,453 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>995000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1162000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1134000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1015000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1171000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1131000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1044000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1009000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1053000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>902000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>758000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>829000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>966000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1017000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1134000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1364000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1448000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1581000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1724000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1712000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1634000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1481000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E58" s="3">
         <v>86000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>157000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>155000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>154000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>153000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>154000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>156000</v>
       </c>
       <c r="L58" s="3">
         <v>156000</v>
       </c>
       <c r="M58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="N58" s="3">
         <v>1554000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2501000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2595000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3841000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2427000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1487000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2885000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1129000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2300000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1744000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1595000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>632000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2551000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2568000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2243000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2750000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2638000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3564000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3699000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4232000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4572000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4597000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4857000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4970000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2949000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2929000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3073000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3028000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3139000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2993000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3234000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3133000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3266000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3260000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3738000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3816000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3534000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3920000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3963000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4848000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4897000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8715000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5781000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5655000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7169000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8300000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6510000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7787000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6634000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5879000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7472000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5703000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7258000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6589000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6495000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5373000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18411000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18591000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19831000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19740000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19899000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19743000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20418000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>21764000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27965000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28397000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27428000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27260000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28574000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27599000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29410000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31105000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31414000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33481000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32394000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33381000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33193000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>34858000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10328000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10262000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10236000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10042000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10022000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9944000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9923000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11761000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11710000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11703000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11556000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11565000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12157000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12139000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12188000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11926000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11823000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11581000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11620000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11084000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11128000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11014000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,79 +4584,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32477000</v>
+      </c>
+      <c r="E66" s="3">
         <v>32669000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33601000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33702000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33884000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34535000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35238000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42240000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45456000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45755000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46153000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47125000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47241000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47525000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48232000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>48910000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>50709000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>50765000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51272000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51054000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50816000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51245000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,79 +4982,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17899000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,79 +5278,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E76" s="3">
         <v>504000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>417000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2219000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2284000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10995000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10374000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12577000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12219000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12282000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11840000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11183000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11706000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11303000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11162000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13689000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13462000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13291000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13470000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13674000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13692000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13543000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5426,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E81" s="3">
         <v>57000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-78000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>511000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>578000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>344000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>599000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>508000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>544000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>506000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>475000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>366000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>377000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>314000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>223000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>302000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>371000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,79 +5609,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>743000</v>
+      </c>
+      <c r="E83" s="3">
         <v>748000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>751000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>755000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>746000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>733000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>796000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>808000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>827000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>808000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>877000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>951000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1041000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1150000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1195000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1193000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1162000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1160000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1210000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1235000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1196000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1188000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6051,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1102000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>784000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>881000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>595000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>841000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1123000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1396000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1375000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1607000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1730000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1639000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1525000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1682000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1794000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1749000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1299000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1909000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1888000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1701000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1182000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,79 +6155,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-753000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-713000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-821000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-843000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-796000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-640000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-833000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-845000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-761000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-577000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-848000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-690000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-646000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-716000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-758000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-988000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-974000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-940000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-957000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-800000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-931000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,79 +6375,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-496000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-698000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1031000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-827000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-789000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-616000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4882000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1864000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-701000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-569000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-763000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-654000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-620000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-675000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-724000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-942000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-959000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-939000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-899000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-954000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-811000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-906000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,16 +6479,17 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-1000</v>
       </c>
       <c r="F96" s="3">
         <v>-1000</v>
@@ -6265,61 +6498,64 @@
         <v>-1000</v>
       </c>
       <c r="H96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-8000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-255000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-254000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-271000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-253000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-266000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-274000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-294000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-272000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-275000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-271000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-291000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-271000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-275000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-269000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-285000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,79 +6773,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>83000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-173000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>158000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-86000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-713000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-776000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-576000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-774000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-597000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-486000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-724000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>57000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-924000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-320000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6673,75 +6921,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-656000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1898000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-119000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-731000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-107000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1042000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-156000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-295000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-242000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>443000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>76000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-120000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>193000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-126000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>286000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>991000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-34000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,337 +656,349 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3221000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3268000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3290000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3517000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3641000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3661000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3738000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3800000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4390000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4612000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4676000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4847000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4887000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4924000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5029000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5125000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5167000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5192000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5228000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5306000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5350000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5427000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1653000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1652000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1737000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1850000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1740000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1817000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1826000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1999000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2058000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1985000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2086000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2151000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2115000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2136000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2231000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2236000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2232000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2235000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2257000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2334000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2243000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2300000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1529000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1615000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1638000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1780000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1921000</v>
       </c>
       <c r="I10" s="3">
         <v>1921000</v>
       </c>
       <c r="J10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="K10" s="3">
         <v>1974000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2391000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2554000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2691000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2761000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2736000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2809000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2893000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2894000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2931000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2960000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2993000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3049000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3016000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3132000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3127000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1013,8 +1025,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,41 +1177,44 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-43000</v>
+        <v>8000</v>
       </c>
       <c r="E14" s="3">
-        <v>-288000</v>
+        <v>-190000</v>
       </c>
       <c r="F14" s="3">
-        <v>1873000</v>
+        <v>-273000</v>
       </c>
       <c r="G14" s="3">
-        <v>-42000</v>
+        <v>1984000</v>
       </c>
       <c r="H14" s="3">
-        <v>8760000</v>
+        <v>37000</v>
       </c>
       <c r="I14" s="3">
-        <v>-581000</v>
+        <v>8795000</v>
       </c>
       <c r="J14" s="3">
+        <v>-452000</v>
+      </c>
+      <c r="K14" s="3">
         <v>3504000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-639000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1206,23 +1225,23 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-8000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2665000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-4000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>79000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
@@ -1230,87 +1249,93 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>6506000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>707000</v>
+      </c>
+      <c r="E15" s="3">
         <v>743000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>748000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>751000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>755000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>746000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>733000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>796000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>808000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>827000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>808000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>877000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>951000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1041000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1150000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1195000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1193000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1162000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1160000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1210000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1235000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1196000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1188000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,156 +1359,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3095000</v>
+        <v>3057000</v>
       </c>
       <c r="E17" s="3">
-        <v>2935000</v>
+        <v>3175000</v>
       </c>
       <c r="F17" s="3">
-        <v>5257000</v>
+        <v>3262000</v>
       </c>
       <c r="G17" s="3">
-        <v>3354000</v>
+        <v>3585000</v>
       </c>
       <c r="H17" s="3">
-        <v>12036000</v>
+        <v>3357000</v>
       </c>
       <c r="I17" s="3">
-        <v>2690000</v>
+        <v>3315000</v>
       </c>
       <c r="J17" s="3">
+        <v>3310000</v>
+      </c>
+      <c r="K17" s="3">
         <v>6797000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2960000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3700000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3593000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3686000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3756000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3918000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4034000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6957000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4275000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4296000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4327000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4459000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4400000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4399000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10926000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>173000</v>
+        <v>164000</v>
       </c>
       <c r="E18" s="3">
-        <v>355000</v>
+        <v>93000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1740000</v>
+        <v>28000</v>
       </c>
       <c r="G18" s="3">
-        <v>287000</v>
+        <v>-68000</v>
       </c>
       <c r="H18" s="3">
-        <v>-8375000</v>
+        <v>284000</v>
       </c>
       <c r="I18" s="3">
-        <v>1048000</v>
+        <v>346000</v>
       </c>
       <c r="J18" s="3">
+        <v>428000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1430000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>912000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1083000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1161000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1131000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1006000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>995000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>892000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>896000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>901000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>847000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>950000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>976000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,378 +1542,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>159000</v>
+        <v>-5000</v>
       </c>
       <c r="E20" s="3">
-        <v>38000</v>
+        <v>-35000</v>
       </c>
       <c r="F20" s="3">
-        <v>-112000</v>
+        <v>-34000</v>
       </c>
       <c r="G20" s="3">
-        <v>-77000</v>
+        <v>-159000</v>
       </c>
       <c r="H20" s="3">
-        <v>-21000</v>
+        <v>41000</v>
       </c>
       <c r="I20" s="3">
-        <v>-89000</v>
+        <v>-49000</v>
       </c>
       <c r="J20" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="K20" s="3">
         <v>95000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-130000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-122000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>70000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-110000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>52000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>26000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>20000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>31000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-44000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>44000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1075000</v>
+        <v>876000</v>
       </c>
       <c r="E21" s="3">
+        <v>871000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>810000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>842000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>998000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1141000</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1101000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>965000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-7650000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1692000</v>
-      </c>
       <c r="J21" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2108000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1617000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1961000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1928000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2044000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2099000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2171000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-617000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2082000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2089000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2042000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2046000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2141000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2216000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E22" s="3">
         <v>373000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>291000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>290000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>295000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>294000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>279000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>280000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>363000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>337000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>352000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>372000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>377000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>384000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>389000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>396000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>409000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>414000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>449000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>487000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>496000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>518000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>523000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-41000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>102000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-85000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>680000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>937000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>453000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>801000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>679000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>716000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>674000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>632000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>480000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>513000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>433000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>349000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>410000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>502000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E24" s="3">
         <v>8000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>45000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-147000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>46000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>169000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-113000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>359000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>109000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>202000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>171000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>172000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>168000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>157000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>81000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>114000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>136000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>119000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>126000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>108000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>131000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>138000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,156 +2002,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-49000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>57000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-78000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>511000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>578000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>344000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>599000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>508000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>544000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>506000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>475000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>366000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>377000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>314000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>223000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>302000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>371000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-49000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>57000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-78000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>511000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>578000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>344000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>599000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>508000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>544000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>506000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>475000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>366000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>377000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>314000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>223000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>302000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>371000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2233,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2229,8 +2289,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2247,11 +2307,14 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,156 +2464,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-159000</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="3">
-        <v>-38000</v>
+        <v>35000</v>
       </c>
       <c r="F32" s="3">
-        <v>112000</v>
+        <v>34000</v>
       </c>
       <c r="G32" s="3">
-        <v>77000</v>
+        <v>159000</v>
       </c>
       <c r="H32" s="3">
-        <v>21000</v>
+        <v>-41000</v>
       </c>
       <c r="I32" s="3">
-        <v>89000</v>
+        <v>49000</v>
       </c>
       <c r="J32" s="3">
+        <v>66000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-95000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>130000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>122000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-70000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>110000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-26000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-20000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-31000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>44000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-49000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>57000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-78000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>511000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>578000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>344000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>599000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>508000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>544000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>506000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>475000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>366000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>377000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>314000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>223000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>302000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>371000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,161 +2695,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-49000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>57000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-78000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>511000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>578000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>344000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>599000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>508000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>544000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>506000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>475000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>366000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>377000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>314000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>223000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>302000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>371000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,82 +2914,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2640000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1495000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1580000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2234000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>311000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>411000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1148000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1251000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>252000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>360000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>366000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>354000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>635000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>935000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>486000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>406000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>526000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1763000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1564000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1690000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1404000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>410000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>441000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2977,327 +3066,342 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1330000</v>
+        <v>1254000</v>
       </c>
       <c r="E43" s="3">
         <v>1351000</v>
       </c>
       <c r="F43" s="3">
-        <v>1610000</v>
+        <v>1369000</v>
       </c>
       <c r="G43" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="H43" s="3">
         <v>1553000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1581000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1450000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1528000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1552000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1529000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1586000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1723000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1605000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1970000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1953000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2035000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2184000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2284000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2281000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2336000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2346000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2590000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2474000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E44" s="3">
         <v>184000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>193000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>209000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>227000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>205000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>223000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>236000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>179000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>151000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>128000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>96000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>103000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>114000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>100000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>105000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>112000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>122000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>119000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>105000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>137000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>151000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>154000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>313000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>312000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>313000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2163000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2220000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2436000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>7399000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>9750000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>9692000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>9363000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>9358000</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>727000</v>
+      </c>
+      <c r="R45" s="3">
+        <v>754000</v>
+      </c>
+      <c r="S45" s="3">
+        <v>630000</v>
+      </c>
+      <c r="T45" s="3">
+        <v>682000</v>
+      </c>
+      <c r="U45" s="3">
+        <v>689000</v>
+      </c>
+      <c r="V45" s="3">
+        <v>726000</v>
+      </c>
+      <c r="W45" s="3">
+        <v>637000</v>
+      </c>
+      <c r="X45" s="3">
+        <v>702000</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>727000</v>
+      </c>
+      <c r="Z45" s="3">
         <v>751000</v>
       </c>
-      <c r="E45" s="3">
-        <v>811000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>722000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2555000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2676000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2584000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2436000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>7399000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>9750000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>9692000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>9363000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>9358000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>727000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>754000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>630000</v>
-      </c>
-      <c r="S45" s="3">
-        <v>682000</v>
-      </c>
-      <c r="T45" s="3">
-        <v>689000</v>
-      </c>
-      <c r="U45" s="3">
-        <v>726000</v>
-      </c>
-      <c r="V45" s="3">
-        <v>637000</v>
-      </c>
-      <c r="W45" s="3">
-        <v>702000</v>
-      </c>
-      <c r="X45" s="3">
-        <v>727000</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>751000</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4736000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3760000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3935000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4775000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4646000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4873000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5405000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5451000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9382000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11790000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11772000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11536000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11701000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3746000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3293000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3176000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3504000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4858000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4690000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4768000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4589000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>3820000</v>
       </c>
       <c r="Z46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3347,156 +3451,165 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20344000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20089000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19908000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20988000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19606000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19432000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19321000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20506000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20713000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20720000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20829000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22346000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20926000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25993000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26091000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28037000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26290000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26079000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27623000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27765000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27595000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27704000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27745000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6931000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7091000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7254000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7434000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9608000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9763000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18691000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18823000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22354000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22575000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22761000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22956000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23147000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26530000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>26738000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>27089000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>30039000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>30372000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>30699000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>31101000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>31386000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>31734000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>32035000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,82 +3759,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1978000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2003000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2076000</v>
       </c>
-      <c r="F52" s="3">
-        <v>821000</v>
-      </c>
       <c r="G52" s="3">
-        <v>2061000</v>
+        <v>709000</v>
       </c>
       <c r="H52" s="3">
-        <v>2100000</v>
+        <v>1898000</v>
       </c>
       <c r="I52" s="3">
-        <v>2113000</v>
+        <v>1941000</v>
       </c>
       <c r="J52" s="3">
+        <v>1957000</v>
+      </c>
+      <c r="K52" s="3">
         <v>832000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2368000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2590000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2675000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1155000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2534000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2678000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2706000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1092000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2766000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2862000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1044000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1108000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1158000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1192000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1188000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,82 +3913,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33989000</v>
+      </c>
+      <c r="E54" s="3">
         <v>32943000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33173000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34018000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35921000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36168000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45530000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45612000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54817000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57675000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58037000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57993000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58308000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58947000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58828000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59394000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62599000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64171000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64056000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64742000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64728000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64508000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64788000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,452 +4050,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>905000</v>
+      </c>
+      <c r="E57" s="3">
         <v>995000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1162000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1134000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1015000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1171000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1131000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1044000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1009000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1053000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>902000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>758000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>829000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>966000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1017000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1134000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1364000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1448000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1581000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1724000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1712000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1634000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1481000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>192000</v>
+        <v>678000</v>
       </c>
       <c r="E58" s="3">
-        <v>86000</v>
+        <v>473000</v>
       </c>
       <c r="F58" s="3">
-        <v>157000</v>
+        <v>368000</v>
       </c>
       <c r="G58" s="3">
-        <v>155000</v>
+        <v>425000</v>
       </c>
       <c r="H58" s="3">
+        <v>451000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>477000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>479000</v>
+      </c>
+      <c r="K58" s="3">
         <v>154000</v>
       </c>
-      <c r="I58" s="3">
-        <v>153000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>154000</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>156000</v>
       </c>
       <c r="M58" s="3">
         <v>156000</v>
       </c>
       <c r="N58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="O58" s="3">
         <v>1554000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2501000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2595000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3841000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2427000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1487000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2885000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1129000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2300000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1744000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1595000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>632000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2551000</v>
+        <v>1421000</v>
       </c>
       <c r="E59" s="3">
-        <v>2568000</v>
+        <v>1446000</v>
       </c>
       <c r="F59" s="3">
-        <v>2243000</v>
+        <v>1598000</v>
       </c>
       <c r="G59" s="3">
-        <v>2750000</v>
+        <v>1111000</v>
       </c>
       <c r="H59" s="3">
-        <v>2638000</v>
+        <v>1582000</v>
       </c>
       <c r="I59" s="3">
-        <v>3564000</v>
+        <v>1534000</v>
       </c>
       <c r="J59" s="3">
+        <v>2560000</v>
+      </c>
+      <c r="K59" s="3">
         <v>3699000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4232000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4572000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4597000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4857000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4970000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2949000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2929000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3073000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3028000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3139000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2993000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3234000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3133000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3266000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3260000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3940000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3738000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3816000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3534000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3920000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3963000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4848000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4897000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8715000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5781000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5655000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7169000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8300000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6510000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7787000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6634000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5879000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7472000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5703000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7258000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6589000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6495000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5373000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18142000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18411000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18591000</v>
       </c>
-      <c r="F61" s="3">
-        <v>19831000</v>
-      </c>
       <c r="G61" s="3">
+        <v>20871000</v>
+      </c>
+      <c r="H61" s="3">
         <v>19740000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19899000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19743000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20418000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21764000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27965000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28397000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27428000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27260000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28574000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27599000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>29410000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31105000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31414000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33481000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32394000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33381000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33193000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>34858000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10328000</v>
+        <v>2637000</v>
       </c>
       <c r="E62" s="3">
-        <v>10262000</v>
+        <v>2637000</v>
       </c>
       <c r="F62" s="3">
-        <v>10236000</v>
+        <v>2641000</v>
       </c>
       <c r="G62" s="3">
-        <v>10042000</v>
+        <v>1610000</v>
       </c>
       <c r="H62" s="3">
-        <v>10022000</v>
+        <v>2626000</v>
       </c>
       <c r="I62" s="3">
-        <v>9944000</v>
+        <v>2633000</v>
       </c>
       <c r="J62" s="3">
+        <v>2578000</v>
+      </c>
+      <c r="K62" s="3">
         <v>9923000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11761000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11710000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11703000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11556000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11565000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12157000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12139000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12188000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11926000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11823000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11581000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11620000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11084000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11128000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11014000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,82 +4741,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33647000</v>
+      </c>
+      <c r="E66" s="3">
         <v>32477000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32669000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33601000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33702000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33884000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34535000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35238000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42240000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45456000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45755000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46153000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47125000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47241000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47525000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>48232000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48910000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>50709000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50765000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51272000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51054000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>50816000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>51245000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4911,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,82 +5155,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18047000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,82 +5463,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E76" s="3">
         <v>466000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>504000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>417000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2219000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2284000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10995000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10374000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12577000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12219000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12282000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11840000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11183000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11706000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11303000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11162000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13689000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13462000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13291000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13470000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13674000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13692000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13543000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,161 +5617,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-49000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>57000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-78000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>511000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>578000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>344000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>599000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>508000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>544000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>506000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>475000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>366000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>377000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>314000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>223000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>302000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>371000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,82 +5807,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>743000</v>
+        <v>484000</v>
       </c>
       <c r="E83" s="3">
-        <v>748000</v>
+        <v>483000</v>
       </c>
       <c r="F83" s="3">
-        <v>751000</v>
+        <v>473000</v>
       </c>
       <c r="G83" s="3">
-        <v>755000</v>
+        <v>520000</v>
       </c>
       <c r="H83" s="3">
-        <v>746000</v>
+        <v>529000</v>
       </c>
       <c r="I83" s="3">
-        <v>733000</v>
+        <v>550000</v>
       </c>
       <c r="J83" s="3">
+        <v>534000</v>
+      </c>
+      <c r="K83" s="3">
         <v>796000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>808000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>827000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>808000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>877000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>951000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1041000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1150000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1195000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1193000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1162000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1160000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1210000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1235000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1196000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1188000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,82 +6267,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2032000</v>
+      </c>
+      <c r="E89" s="3">
         <v>511000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1102000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>784000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>881000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>595000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>841000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1123000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1396000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1375000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1607000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1730000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1639000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1525000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1682000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1794000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1749000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1299000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1909000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1888000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1701000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1182000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,82 +6375,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-850000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-753000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-713000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-821000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-843000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-796000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-640000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-833000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-845000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-761000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-577000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-848000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-690000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-646000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-716000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-758000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-988000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-974000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-940000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-957000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-800000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-931000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,82 +6604,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-805000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-496000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-698000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1031000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-827000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-789000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-616000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4882000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1864000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-701000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-569000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-763000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-654000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-620000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-675000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-724000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-942000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-959000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-939000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-899000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-954000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-811000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-906000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6712,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6489,73 +6722,76 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-1000</v>
+        <v>3000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="I96" s="3">
-        <v>-8000</v>
+        <v>1000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-255000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-254000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-271000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-253000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-266000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-274000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-294000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-272000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-275000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-271000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-291000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-271000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-275000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-269000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-285000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,105 +7018,111 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>83000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-173000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>158000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-86000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-713000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-776000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-576000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-774000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-597000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-486000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-724000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>57000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-924000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-320000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6924,78 +7172,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1146000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-85000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-656000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1898000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-119000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-731000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-107000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1042000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-156000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-295000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-242000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>443000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>76000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-120000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>193000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-126000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>286000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>991000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,349 +656,361 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3329000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3221000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3268000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3290000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3517000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3641000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3661000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3738000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3800000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4390000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4612000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4676000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4847000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4887000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4924000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5029000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5125000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5167000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5192000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5228000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5306000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5350000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5375000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5427000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1706000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1692000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1653000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1652000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1737000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1850000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1740000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1817000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1826000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1999000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2058000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1985000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2086000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2151000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2115000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2136000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2231000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2236000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2232000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2235000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2257000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2334000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2243000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2300000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1623000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1529000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1615000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1638000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1780000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1921000</v>
       </c>
       <c r="J10" s="3">
         <v>1921000</v>
       </c>
       <c r="K10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="L10" s="3">
         <v>1974000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2391000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2554000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2691000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2761000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2736000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2809000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2893000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2894000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2931000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2960000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2993000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3049000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3016000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3132000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3127000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1038,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1116,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1180,44 +1196,47 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E14" s="3">
         <v>8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-190000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-273000</v>
       </c>
-      <c r="G14" s="3">
-        <v>1984000</v>
-      </c>
       <c r="H14" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="I14" s="3">
         <v>37000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8795000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-452000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3504000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-639000</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1228,23 +1247,23 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-8000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2665000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-4000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>79000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1252,90 +1271,96 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>6506000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>758000</v>
+      </c>
+      <c r="E15" s="3">
         <v>707000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>743000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>748000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>751000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>755000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>746000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>733000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>796000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>808000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>827000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>808000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>877000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>951000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1041000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1150000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1195000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1193000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1162000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1160000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1210000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1235000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1196000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1188000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1360,162 +1385,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3057000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3175000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3262000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3585000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3357000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3315000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3310000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6797000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2960000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3700000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3593000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3686000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3756000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3918000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4034000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6957000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4275000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4296000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4327000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4459000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4400000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4399000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10926000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E18" s="3">
         <v>164000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>93000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-68000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>284000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>346000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>428000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1430000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>912000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1083000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1161000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1131000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1006000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>995000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>892000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>896000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>901000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>847000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>950000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>976000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1543,393 +1575,409 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-250000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-35000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-34000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-159000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="I20" s="3">
         <v>41000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-49000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-66000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>95000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-130000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-122000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>70000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-110000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>52000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>26000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>20000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>31000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-19000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>44000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1026000</v>
+      </c>
+      <c r="E21" s="3">
         <v>876000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>871000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>810000</v>
       </c>
-      <c r="G21" s="3">
-        <v>842000</v>
-      </c>
       <c r="H21" s="3">
+        <v>885000</v>
+      </c>
+      <c r="I21" s="3">
         <v>998000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1141000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1227000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2108000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1617000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1961000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1928000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2044000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2099000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2171000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-617000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2082000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2089000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2042000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2046000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2141000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2216000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E22" s="3">
         <v>351000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>373000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>291000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>290000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>295000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>294000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>279000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>280000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>363000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>337000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>352000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>372000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>377000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>384000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>389000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>396000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>409000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>414000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>449000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>487000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>496000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>518000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>523000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-172000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-41000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>102000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-85000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>680000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>937000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>453000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>801000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>679000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>716000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>674000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>632000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>480000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>513000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>433000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>349000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>410000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>502000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-24000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>45000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-147000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>46000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>169000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-113000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>359000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>109000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>202000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>171000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>172000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>168000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>157000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>81000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>114000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>136000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>119000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>126000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>108000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>131000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>138000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2005,162 +2053,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-148000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-49000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>57000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-78000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>511000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>578000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>344000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>599000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>508000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>544000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>506000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>475000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>366000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>377000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>314000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>223000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>302000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>371000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-148000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-49000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>57000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-78000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>511000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>578000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>344000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>599000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>508000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>544000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>506000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>475000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>366000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>377000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>314000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>223000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>302000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>371000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2236,8 +2293,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2292,8 +2352,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2310,11 +2370,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2390,8 +2453,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2467,162 +2533,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>35000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>34000</v>
       </c>
-      <c r="G32" s="3">
-        <v>159000</v>
-      </c>
       <c r="H32" s="3">
+        <v>202000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-41000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>49000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>66000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-95000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>130000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>122000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-70000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>110000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>38000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-52000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-26000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-20000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-31000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>19000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>44000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-148000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-49000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>57000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-78000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>511000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>578000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>344000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>599000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>508000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>544000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>506000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>475000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>366000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>377000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>314000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>223000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>302000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>371000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2698,167 +2773,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-148000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-49000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>57000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-78000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>511000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>578000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>344000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>599000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>508000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>544000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>506000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>475000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>366000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>377000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>314000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>223000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>302000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>371000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2886,8 +2970,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2915,85 +3000,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2640000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1495000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1580000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2234000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>311000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>411000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1148000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1251000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>252000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>360000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>366000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>354000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>635000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>935000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>486000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>406000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>526000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1763000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1564000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1690000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1404000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>410000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>441000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3069,316 +3158,331 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1730000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1254000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1351000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1369000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1624000</v>
-      </c>
       <c r="H43" s="3">
+        <v>1610000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1553000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1581000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1450000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1528000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1552000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1529000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1586000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1723000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1605000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1970000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1953000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2035000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2184000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2284000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2281000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2336000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2346000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2590000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2474000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E44" s="3">
         <v>173000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>184000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>193000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>209000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>227000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>205000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>223000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>236000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>179000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>151000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>128000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>96000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>103000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>114000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>100000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>105000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>112000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>122000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>119000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>105000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>137000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>151000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>154000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E45" s="3">
         <v>312000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>313000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>312000</v>
       </c>
-      <c r="G45" s="3">
-        <v>313000</v>
-      </c>
       <c r="H45" s="3">
+        <v>327000</v>
+      </c>
+      <c r="I45" s="3">
         <v>2163000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2220000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2174000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2436000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7399000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9750000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9692000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9363000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9358000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>727000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>754000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>630000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>682000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>689000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>726000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>637000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>702000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>727000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>751000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4394000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4736000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3760000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3935000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4775000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4646000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4873000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5405000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5451000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9382000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11790000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11772000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11536000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11701000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3746000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3293000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3176000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3504000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4858000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4690000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4768000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4589000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>3820000</v>
       </c>
       <c r="AA46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3403,8 +3507,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3454,162 +3558,171 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21540000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20344000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20089000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19908000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20988000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19606000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19432000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19321000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20506000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20713000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20720000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20829000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22346000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20926000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25993000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26091000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>28037000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26290000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26079000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27623000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27765000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27595000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27704000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>27745000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6770000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6931000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7091000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7254000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7434000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9608000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9763000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18691000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18823000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22354000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22575000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22761000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22956000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23147000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>26530000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>26738000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>27089000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>30039000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>30372000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>30699000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>31101000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>31386000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>31734000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>32035000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3685,8 +3798,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3762,85 +3878,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>792000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1978000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2003000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2076000</v>
       </c>
-      <c r="G52" s="3">
-        <v>709000</v>
-      </c>
       <c r="H52" s="3">
+        <v>821000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1898000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1941000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1957000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>832000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2368000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2590000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2675000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1155000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2534000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2678000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2706000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1092000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2766000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2862000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1044000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1108000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1158000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1192000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3916,85 +4038,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33496000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33989000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32943000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33173000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34018000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35921000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36168000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45530000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45612000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>54817000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57675000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58037000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57993000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58308000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58947000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58828000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>59394000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>62599000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64171000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64056000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64742000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64728000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64508000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64788000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4022,8 +4150,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4051,470 +4180,489 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>749000</v>
+      </c>
+      <c r="E57" s="3">
         <v>905000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>995000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1162000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1134000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1015000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1171000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1131000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1044000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1009000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1053000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>902000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>758000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>829000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>966000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1017000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1134000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1364000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1448000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1581000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1724000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1712000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1634000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>665000</v>
+      </c>
+      <c r="E58" s="3">
         <v>678000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>473000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>368000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>425000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>451000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>477000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>479000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>154000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>156000</v>
       </c>
       <c r="N58" s="3">
         <v>156000</v>
       </c>
       <c r="O58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="P58" s="3">
         <v>1554000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2501000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2595000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3841000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2427000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1487000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2885000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1129000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2300000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1744000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1595000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>632000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1312000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1421000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1446000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1598000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1111000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1582000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1534000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2560000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3699000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4232000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4572000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4597000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4857000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4970000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2949000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2929000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3073000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3028000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3139000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2993000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3234000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3133000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3266000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3260000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3639000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3940000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3738000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3816000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3534000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3920000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3963000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4848000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4897000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8715000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5781000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5655000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7169000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8300000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6510000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7787000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6634000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5879000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7472000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5703000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7258000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6589000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6495000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5373000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18453000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18142000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18411000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18591000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20871000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19740000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19899000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19743000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20418000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21764000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27965000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28397000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27428000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27260000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28574000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27599000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29410000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31105000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31414000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33481000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32394000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33381000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33193000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>34858000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2637000</v>
+        <v>2112000</v>
       </c>
       <c r="E62" s="3">
         <v>2637000</v>
       </c>
       <c r="F62" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="G62" s="3">
         <v>2641000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1610000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2626000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2633000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2578000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9923000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11761000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11710000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11703000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11556000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11565000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12157000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12139000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12188000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11926000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11823000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11581000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11620000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11084000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11128000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11014000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4590,8 +4738,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4667,8 +4818,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4744,85 +4898,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33032000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33647000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32477000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32669000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33601000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33702000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33884000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34535000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35238000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>42240000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>45456000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45755000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46153000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47125000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47241000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47525000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48232000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48910000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50709000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50765000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51272000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51054000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50816000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>51245000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4850,8 +5010,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4927,8 +5088,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5004,8 +5168,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5081,8 +5248,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5158,85 +5328,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17962000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-18047000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5312,8 +5488,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5389,8 +5568,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5466,85 +5648,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E76" s="3">
         <v>342000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>466000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>504000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>417000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2219000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2284000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10995000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10374000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12577000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12219000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12282000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11840000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11183000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11706000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11303000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11162000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13689000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13462000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13291000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13470000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13674000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13692000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13543000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5620,167 +5808,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-148000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-49000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>57000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-78000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>511000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>578000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>344000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>599000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>508000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>544000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>506000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>475000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>366000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>377000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>314000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>223000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>302000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>371000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5808,85 +6005,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E83" s="3">
         <v>484000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>483000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>473000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>520000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>529000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>550000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>534000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>796000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>808000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>827000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>808000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>877000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>951000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1041000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1150000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1195000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1193000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1162000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1160000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1210000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1235000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1196000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1188000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5962,8 +6163,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6039,8 +6243,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6116,8 +6323,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6193,8 +6403,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6270,85 +6483,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>688000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2032000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>511000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1102000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>784000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>881000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>595000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>841000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1123000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1396000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1375000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1607000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1730000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1639000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1525000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1682000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1794000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1749000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1299000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1909000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1888000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1701000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6376,85 +6595,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-850000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-753000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-713000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-821000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-843000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-796000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-640000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-833000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-845000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-761000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-577000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-848000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-690000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-646000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-716000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-758000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-988000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-974000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-940000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-957000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6530,8 +6753,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6607,85 +6833,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-831000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-805000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-496000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-698000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1031000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-827000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-789000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-616000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4882000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1864000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-701000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-569000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-763000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-654000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-620000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-675000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-724000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-942000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-959000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-939000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-899000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-954000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-811000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6713,8 +6945,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6725,10 +6958,10 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>3000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>1000</v>
       </c>
       <c r="H96" s="3">
         <v>1000</v>
@@ -6737,61 +6970,64 @@
         <v>1000</v>
       </c>
       <c r="J96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K96" s="3">
         <v>8000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-255000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-254000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-271000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-253000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-266000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-274000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-294000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-272000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-275000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-271000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-291000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-271000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-275000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-269000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-285000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6867,8 +7103,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6944,8 +7183,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7021,85 +7263,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-610000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-81000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>83000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-173000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>158000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-86000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-713000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-776000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-576000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-774000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-597000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-486000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-724000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>57000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-924000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7124,8 +7372,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7175,81 +7423,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-753000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1146000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-85000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-656000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1898000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-119000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-731000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-107000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1042000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-156000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-295000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-242000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>443000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>76000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-120000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>193000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-126000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>286000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>991000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,361 +656,373 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3182000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3329000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3221000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3268000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3290000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3517000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3641000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3661000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3738000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3800000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4390000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4612000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4676000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4847000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4887000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4924000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5029000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5125000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5167000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5192000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5228000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5306000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5350000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5427000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1706000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1692000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1653000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1652000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1737000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1850000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1740000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1817000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1826000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1999000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2058000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1985000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2086000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2151000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2115000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2136000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2231000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2236000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2232000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2235000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2257000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2334000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2243000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2300000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1495000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1623000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1529000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1615000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1638000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1780000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1921000</v>
       </c>
       <c r="K10" s="3">
         <v>1921000</v>
       </c>
       <c r="L10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="M10" s="3">
         <v>1974000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2391000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2554000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2691000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2761000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2736000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2809000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2893000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2894000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2931000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2960000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2993000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3049000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3016000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3132000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3127000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1039,8 +1051,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1119,8 +1132,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1199,47 +1215,50 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E14" s="3">
         <v>59000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-190000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-273000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2006000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>37000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8795000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-452000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3504000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-639000</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1250,23 +1269,23 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-8000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2665000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-4000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>79000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1274,93 +1293,99 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>6506000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E15" s="3">
         <v>758000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>707000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>743000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>748000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>751000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>755000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>746000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>733000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>796000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>808000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>827000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>808000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>877000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>951000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1041000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1150000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1195000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1193000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1162000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1160000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1210000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1235000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1196000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1386,168 +1411,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3121000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3311000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3057000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3175000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3262000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3585000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3357000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3315000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3310000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6797000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2960000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3700000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3593000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3686000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3756000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3918000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4034000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6957000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4275000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4296000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4327000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4459000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4400000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4399000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10926000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E18" s="3">
         <v>18000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>164000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>93000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>28000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-68000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>284000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>346000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>428000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1430000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>912000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1083000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1161000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1131000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1006000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>995000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>892000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>896000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>901000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>847000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>950000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>976000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1576,408 +1608,424 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-250000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-35000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-34000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-202000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>41000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-49000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-66000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>95000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-130000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-122000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>70000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-110000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-38000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>52000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>26000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>31000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>44000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>829000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1026000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>876000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>871000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>810000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>885000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>998000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1141000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1227000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2108000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1617000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1961000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1928000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2044000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2099000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2171000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-617000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2082000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2089000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2042000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2046000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2141000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2216000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E22" s="3">
         <v>357000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>351000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>373000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>291000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>290000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>295000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>294000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>279000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>280000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>363000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>337000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>352000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>372000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>377000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>384000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>389000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>396000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>409000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>414000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>449000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>487000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>496000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>518000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>523000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-245000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-119000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-172000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>102000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-85000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>680000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>937000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>453000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>801000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>679000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>716000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>674000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>632000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>480000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>513000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>433000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>349000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>410000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>502000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-204000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-24000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>45000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-147000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>46000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>169000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-113000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>359000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>109000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>202000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>171000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>172000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>168000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>157000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>81000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>114000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>136000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>119000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>126000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>108000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>131000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>138000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2056,168 +2104,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E26" s="3">
         <v>85000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-148000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-49000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>57000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-78000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>511000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>578000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>344000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>599000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>508000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>544000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>506000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>475000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>366000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>377000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>314000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>223000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>302000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>371000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E27" s="3">
         <v>85000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-148000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-49000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>57000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-78000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>511000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>578000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>344000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>599000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>508000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>544000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>506000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>475000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>366000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>377000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>314000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>223000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>302000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>371000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2296,8 +2353,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2355,8 +2415,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2373,11 +2433,14 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2456,8 +2519,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2536,168 +2602,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E32" s="3">
         <v>250000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>35000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>34000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>202000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-41000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>49000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>66000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-95000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>130000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>122000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-70000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>110000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>38000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-52000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-26000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-31000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>44000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E33" s="3">
         <v>85000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-148000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-49000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>57000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-78000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>511000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>578000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>344000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>599000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>508000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>544000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>506000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>475000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>366000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>377000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>314000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>223000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>302000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>371000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2776,173 +2851,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E35" s="3">
         <v>85000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-148000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-49000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>57000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-78000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>511000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>578000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>344000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>599000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>508000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>544000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>506000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>475000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>366000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>377000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>314000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>223000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>302000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>371000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2971,8 +3055,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3001,88 +3086,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1889000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2640000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1495000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1580000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2234000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>311000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>411000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1148000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1251000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>252000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>360000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>366000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>354000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>635000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>935000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>486000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>406000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>526000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1763000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1564000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1690000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1404000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>410000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>441000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3161,328 +3250,343 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1730000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1254000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1351000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1369000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1610000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1553000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1581000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1450000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1528000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1552000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1529000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1586000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1723000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1605000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1970000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1953000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2035000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2184000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2284000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2281000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2336000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2346000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2590000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2474000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E44" s="3">
         <v>146000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>173000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>184000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>193000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>209000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>227000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>205000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>223000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>236000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>179000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>151000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>128000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>96000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>103000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>114000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>100000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>105000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>112000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>122000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>119000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>105000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>137000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>151000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>154000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E45" s="3">
         <v>257000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>312000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>313000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>312000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>327000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2163000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2220000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2174000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2436000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7399000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9750000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9692000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9363000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9358000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>727000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>754000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>630000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>682000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>689000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>726000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>637000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>702000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>727000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>751000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4277000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4394000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4736000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3760000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3935000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4775000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4646000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4873000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5405000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5451000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9382000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11790000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11772000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11536000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11701000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3746000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3293000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3176000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3504000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4858000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4690000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4768000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4589000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>3820000</v>
       </c>
       <c r="AB46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3510,8 +3614,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3561,168 +3665,177 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20568000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21540000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20344000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20089000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19908000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20988000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19606000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19432000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19321000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20506000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20713000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20720000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20829000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22346000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20926000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25993000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26091000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28037000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26290000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26079000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27623000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27765000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27595000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>27704000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>27745000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6624000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6770000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6931000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7091000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7254000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7434000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9608000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9763000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18691000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18823000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22354000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22575000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22761000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22956000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23147000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>26530000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>26738000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>27089000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>30039000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>30372000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>30699000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>31101000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>31386000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>31734000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>32035000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3801,8 +3914,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3881,88 +3997,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2069000</v>
+      </c>
+      <c r="E52" s="3">
         <v>792000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1978000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2003000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2076000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>821000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1898000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1941000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1957000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>832000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2368000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2590000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2675000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1155000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2534000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2678000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2706000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1092000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2766000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2862000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1044000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1108000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1158000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1192000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4041,88 +4163,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33538000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33496000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33989000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32943000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33173000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34018000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35921000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36168000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45530000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45612000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>54817000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57675000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58037000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57993000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58308000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58947000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58828000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>59394000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>62599000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64171000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64056000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64742000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64728000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64508000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>64788000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4151,8 +4279,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4181,488 +4310,507 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>773000</v>
+      </c>
+      <c r="E57" s="3">
         <v>749000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>905000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>995000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1162000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1134000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1015000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1171000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1131000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1044000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1009000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1053000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>902000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>758000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>829000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>966000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1017000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1134000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1364000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1448000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1581000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1724000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1712000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1634000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>593000</v>
+      </c>
+      <c r="E58" s="3">
         <v>665000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>678000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>473000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>368000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>425000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>451000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>477000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>479000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>154000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>156000</v>
       </c>
       <c r="O58" s="3">
         <v>156000</v>
       </c>
       <c r="P58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1554000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2501000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2595000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3841000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2427000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1487000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2885000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1129000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2300000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1744000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1595000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>632000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1312000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1421000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1446000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1598000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1111000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1582000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1534000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2560000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3699000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4232000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4572000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4597000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4857000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4970000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2949000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2929000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3073000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3028000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3139000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2993000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3234000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3133000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3266000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3260000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3545000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3639000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3940000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3738000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3816000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3534000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3920000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3963000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4848000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4897000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8715000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5781000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5655000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7169000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8300000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6510000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7787000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6634000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5879000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7472000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5703000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7258000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6589000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6495000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5373000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17334000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18453000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18142000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18411000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18591000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20871000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19740000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19899000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19743000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20418000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21764000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27965000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28397000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27428000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27260000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28574000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>27599000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29410000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31105000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31414000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33481000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32394000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33381000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33193000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34858000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3236000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2112000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2637000</v>
       </c>
       <c r="F62" s="3">
         <v>2637000</v>
       </c>
       <c r="G62" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="H62" s="3">
         <v>2641000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1610000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2626000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2633000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2578000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9923000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11761000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11710000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11703000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11556000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11565000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12157000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12139000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12188000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11926000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11823000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11581000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11620000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11084000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11128000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11014000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4741,8 +4889,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4821,8 +4972,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4901,88 +5055,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33249000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33032000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33647000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32477000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32669000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33601000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33702000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33884000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34535000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35238000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>42240000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45456000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45755000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46153000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47125000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47241000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47525000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48232000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48910000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50709000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50765000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51272000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>51054000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50816000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>51245000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5011,8 +5171,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5091,8 +5252,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5171,8 +5335,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5251,8 +5418,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5331,88 +5501,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18163000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17962000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-18047000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5491,8 +5667,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5571,8 +5750,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5651,88 +5833,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>289000</v>
+      </c>
+      <c r="E76" s="3">
         <v>464000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>342000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>466000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>504000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>417000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2219000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2284000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10995000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10374000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12577000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12219000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12282000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11840000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11183000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11706000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11303000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11162000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13689000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13462000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13291000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13470000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13674000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13692000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13543000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5811,173 +5999,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E81" s="3">
         <v>85000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-148000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-49000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>57000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-78000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>511000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>578000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>344000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>599000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>508000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>544000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>506000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>475000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>366000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>377000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>314000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>223000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>302000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>371000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6006,88 +6203,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>476000</v>
+      </c>
+      <c r="E83" s="3">
         <v>492000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>484000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>483000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>473000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>520000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>529000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>550000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>534000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>796000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>808000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>827000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>808000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>877000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>951000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1041000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1150000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1195000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1193000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1162000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1160000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1210000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1235000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1196000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6166,8 +6367,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6246,8 +6450,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6326,8 +6533,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6406,8 +6616,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6486,88 +6699,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E89" s="3">
         <v>688000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2032000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>511000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1102000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>784000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>881000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>595000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>841000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1123000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1396000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1375000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1607000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1730000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1639000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1525000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1682000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1794000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1749000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1299000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1909000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1888000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1701000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6596,88 +6815,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-791000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-915000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-850000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-753000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-713000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-821000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-843000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-796000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-640000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-833000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-845000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-761000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-577000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-848000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-690000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-646000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-716000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-758000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-988000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-974000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-940000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-957000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-800000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6756,8 +6979,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6836,88 +7062,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-769000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-831000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-805000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-496000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-698000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1031000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-827000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-789000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-616000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4882000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1864000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-701000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-569000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-763000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-654000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-620000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-675000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-724000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-942000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-959000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-939000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-899000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-954000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6946,13 +7178,14 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -6961,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>3000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>1000</v>
       </c>
       <c r="I96" s="3">
         <v>1000</v>
@@ -6973,61 +7206,64 @@
         <v>1000</v>
       </c>
       <c r="K96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L96" s="3">
         <v>8000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-255000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-254000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-271000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-253000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-266000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-274000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-294000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-272000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-275000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-271000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-291000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-271000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-275000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-285000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7106,8 +7342,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7186,8 +7425,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7266,88 +7508,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-314000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-610000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-81000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>83000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-173000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>158000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-86000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-713000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-776000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-576000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-774000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-597000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-486000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-724000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>57000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-924000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7375,8 +7623,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7426,84 +7674,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-753000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1146000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-85000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-656000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1898000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-119000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-731000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-107000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1042000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-156000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-295000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-242000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>443000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>76000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-120000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>193000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-126000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>286000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>991000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,373 +656,385 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3092000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3182000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3329000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3221000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3268000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3290000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3517000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3641000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3661000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3738000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3800000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4390000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4612000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4676000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4847000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4887000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4924000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5029000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5125000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5167000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5192000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5228000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5306000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5350000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5427000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1687000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1706000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1692000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1653000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1652000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1737000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1850000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1740000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1817000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1826000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1999000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2058000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1985000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2086000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2151000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2115000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2136000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2231000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2236000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2232000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2235000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2257000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2334000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2243000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2300000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1468000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1495000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1623000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1529000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1615000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1638000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1780000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1921000</v>
       </c>
       <c r="L10" s="3">
         <v>1921000</v>
       </c>
       <c r="M10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="N10" s="3">
         <v>1974000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2391000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2554000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2691000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2761000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2736000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2809000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2893000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2894000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2931000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2960000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2993000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3049000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3016000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3132000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3127000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,8 +1064,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1135,8 +1148,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,50 +1234,53 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>864000</v>
+      </c>
+      <c r="E14" s="3">
         <v>35000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>59000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-190000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-273000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2006000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>37000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8795000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-452000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3504000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-639000</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1272,23 +1291,23 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-8000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2665000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-4000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>7000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>79000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
@@ -1296,96 +1315,102 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>6506000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>688000</v>
+      </c>
+      <c r="E15" s="3">
         <v>713000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>758000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>707000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>743000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>748000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>751000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>755000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>746000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>733000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>796000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>808000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>827000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>808000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>877000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>951000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1041000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1150000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1195000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1193000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1162000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1160000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1210000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1235000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1196000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1412,174 +1437,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3113000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3121000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3311000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3057000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3175000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3262000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3585000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3357000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3315000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3310000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6797000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2960000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3700000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3593000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3686000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3756000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3918000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4034000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6957000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4275000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4296000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4327000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4459000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4400000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4399000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10926000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E18" s="3">
         <v>61000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>164000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>93000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>28000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-68000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>284000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>346000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>428000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1430000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>912000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1083000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1161000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1131000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1006000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>995000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>892000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>896000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>901000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>847000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>950000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>976000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,423 +1641,439 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-55000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-250000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-35000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-34000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-202000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>41000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-49000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-66000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>95000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-130000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-122000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>70000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-110000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-38000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>52000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>26000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>31000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>44000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E21" s="3">
         <v>829000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1026000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>876000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>871000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>810000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>885000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>998000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1141000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1227000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2108000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1617000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1961000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1928000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2044000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2099000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2171000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-617000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2082000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2089000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2042000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2046000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2141000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2216000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E22" s="3">
         <v>347000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>357000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>351000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>373000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>291000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>290000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>295000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>294000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>279000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>280000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>363000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>337000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>352000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>372000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>377000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>384000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>389000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>396000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>409000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>414000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>449000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>487000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>496000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>518000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>523000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1149000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-245000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-119000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-172000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>102000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-85000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>680000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>937000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>453000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>801000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>679000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>716000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>674000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>632000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>480000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>513000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>433000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>349000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>410000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>502000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-234000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-44000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-204000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-24000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>45000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-147000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>46000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>169000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-113000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>359000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>109000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>202000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>171000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>172000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>168000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>157000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>81000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>114000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>136000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>119000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>126000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>108000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>131000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>138000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,174 +2155,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-201000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>85000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-148000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-49000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>57000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-78000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>511000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>578000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>344000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>599000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>508000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>544000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>506000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>475000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>366000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>377000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>314000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>223000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>302000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>371000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-201000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>85000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-148000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-49000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>57000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-78000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>511000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>578000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>344000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>599000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>508000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>544000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>506000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>475000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>366000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>377000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>314000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>223000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>302000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>371000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,8 +2413,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2418,8 +2478,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2436,11 +2496,14 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,8 +2585,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,174 +2671,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E32" s="3">
         <v>55000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>250000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>35000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>34000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>202000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-41000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>49000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>66000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-95000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>130000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>122000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>110000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>38000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-52000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-26000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-31000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>44000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-201000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>85000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-148000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-49000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>57000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-78000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>511000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>578000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>344000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>599000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>508000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>544000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>506000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>475000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>366000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>377000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>314000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>223000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>302000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>371000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,179 +2929,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-201000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>85000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-148000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-49000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>57000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-78000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>511000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>578000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>344000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>599000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>508000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>544000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>506000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>475000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>366000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>377000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>314000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>223000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>302000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>371000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3056,8 +3140,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3087,91 +3172,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1568000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1889000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2640000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1495000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1580000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2234000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>311000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>411000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1148000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1251000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>252000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>360000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>366000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>354000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>635000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>935000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>486000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>406000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>526000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1763000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1564000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1690000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1404000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>410000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>441000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3253,340 +3342,355 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1580000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1730000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1254000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1351000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1369000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1610000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1553000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1581000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1450000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1528000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1552000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1529000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1586000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1723000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1605000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1970000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1953000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2035000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2184000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2284000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2281000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2336000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2346000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2590000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E44" s="3">
         <v>124000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>146000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>173000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>184000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>193000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>209000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>227000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>205000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>223000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>236000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>179000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>151000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>128000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>96000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>103000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>114000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>100000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>105000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>112000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>122000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>119000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>105000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>137000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>151000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>154000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E45" s="3">
         <v>262000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>257000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>312000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>313000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>312000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>327000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2163000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2220000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2174000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2436000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7399000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9750000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9692000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9363000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9358000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>727000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>754000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>630000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>682000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>689000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>726000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>637000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>702000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>727000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>751000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7737000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4277000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4394000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4736000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3760000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3935000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4775000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4646000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4873000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5405000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5451000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9382000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11790000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11772000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11536000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11701000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3746000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3293000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3176000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3504000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4858000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4690000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4768000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4589000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>3820000</v>
       </c>
       <c r="AC46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3617,8 +3721,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3668,174 +3772,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18665000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20568000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21540000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20344000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20089000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19908000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20988000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19606000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19432000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19321000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20506000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20713000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20720000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20829000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22346000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20926000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25993000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26091000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>28037000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26290000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26079000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27623000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27765000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>27595000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>27704000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27745000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4525000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6624000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6770000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6931000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7091000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7254000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7434000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9608000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9763000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18691000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18823000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22354000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22575000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22761000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22956000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23147000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>26530000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>26738000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>27089000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>30039000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>30372000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>30699000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>31101000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>31386000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>31734000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>32035000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,8 +4030,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,91 +4116,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2049000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2069000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>792000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1978000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2003000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2076000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>821000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1898000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1941000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1957000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>832000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2368000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2590000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2675000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1155000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2534000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2678000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2706000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1092000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2766000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2862000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1044000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1108000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1158000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1192000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,91 +4288,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32976000</v>
+      </c>
+      <c r="E54" s="3">
         <v>33538000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33496000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33989000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32943000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33173000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>34018000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35921000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36168000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45530000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>45612000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>54817000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57675000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58037000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57993000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58308000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58947000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58828000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59394000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>62599000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64171000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64056000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64742000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64728000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>64508000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>64788000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4280,8 +4408,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4311,506 +4440,525 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>831000</v>
+      </c>
+      <c r="E57" s="3">
         <v>773000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>749000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>905000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>995000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1162000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1134000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1015000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1171000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1131000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1044000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1009000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1053000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>902000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>758000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>829000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>966000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1017000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1134000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1364000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1448000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1581000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1724000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1712000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1634000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E58" s="3">
         <v>593000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>665000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>678000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>473000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>368000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>425000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>451000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>477000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>479000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>154000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>156000</v>
       </c>
       <c r="P58" s="3">
         <v>156000</v>
       </c>
       <c r="Q58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="R58" s="3">
         <v>1554000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2501000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2595000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3841000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2427000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1487000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2885000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1129000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2300000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1744000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1595000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>632000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1456000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1379000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1312000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1421000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1446000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1598000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1111000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1582000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1534000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2560000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3699000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4232000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4572000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4597000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4857000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4970000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2949000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2929000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3073000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3028000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3139000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2993000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3234000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3133000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3266000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3260000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3632000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3545000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3639000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3940000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3738000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3816000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3534000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3920000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3963000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4848000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4897000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8715000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5781000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5655000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7169000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8300000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6510000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7787000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6634000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5879000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7472000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5703000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7258000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6589000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6495000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5373000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17565000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17334000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18453000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18142000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18411000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18591000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20871000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19740000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19899000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19743000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20418000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21764000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27965000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28397000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27428000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27260000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28574000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27599000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29410000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31105000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>31414000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33481000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32394000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33381000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33193000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34858000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3276000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3236000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2112000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2637000</v>
       </c>
       <c r="G62" s="3">
         <v>2637000</v>
       </c>
       <c r="H62" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2641000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1610000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2626000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2633000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2578000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9923000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11761000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11710000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11703000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11556000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11565000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12157000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12139000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12188000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11926000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11823000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11581000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11620000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11084000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11128000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11014000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,8 +5040,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,8 +5126,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,91 +5212,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33571000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33249000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33032000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33647000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32477000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32669000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33601000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33702000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33884000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34535000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35238000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42240000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45456000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45755000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>46153000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47125000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47241000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>47525000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48232000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48910000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50709000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>50765000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>51272000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>51054000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50816000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>51245000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5332,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,8 +5416,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,8 +5502,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,8 +5588,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,91 +5674,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-19078000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-18163000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17962000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-18047000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,8 +5846,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,8 +5932,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,91 +6018,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-595000</v>
+      </c>
+      <c r="E76" s="3">
         <v>289000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>464000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>342000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>466000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>504000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>417000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2219000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2284000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10995000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10374000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12577000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12219000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12282000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11840000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11183000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11706000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11303000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11162000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13689000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13462000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13291000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13470000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13674000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13692000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13543000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,179 +6190,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-915000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-201000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>85000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-148000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-49000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>57000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-78000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>511000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>578000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>344000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>599000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>508000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>544000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>506000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>475000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>366000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>377000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>314000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>223000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>302000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>371000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6204,91 +6401,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E83" s="3">
         <v>476000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>492000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>484000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>483000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>473000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>520000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>529000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>550000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>534000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>796000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>808000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>827000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>808000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>877000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>951000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1041000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1150000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1195000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1193000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1162000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1160000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1210000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1235000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1196000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1188000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,8 +6571,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,8 +6657,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,8 +6743,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,8 +6829,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,91 +6915,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1095000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>688000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2032000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>511000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1102000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>784000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>881000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>595000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>841000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1123000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1396000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1375000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1607000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1730000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1639000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1525000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1682000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1794000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1749000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1299000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1909000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1888000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1701000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6816,91 +7035,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-891000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-791000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-915000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-850000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-753000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-713000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-821000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-843000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-796000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-640000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-833000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-845000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-761000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-577000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-848000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-690000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-646000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-716000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-758000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-988000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-974000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-940000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-957000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-800000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,8 +7205,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,91 +7291,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-873000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-769000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-831000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-805000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-496000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-698000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1031000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-827000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-789000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-616000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4882000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1864000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-701000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-569000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-763000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-654000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-620000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-675000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-724000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-942000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-959000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-939000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-899000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7179,28 +7411,29 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>1000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>3000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>1000</v>
       </c>
       <c r="J96" s="3">
         <v>1000</v>
@@ -7209,61 +7442,64 @@
         <v>1000</v>
       </c>
       <c r="L96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M96" s="3">
         <v>8000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-255000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-254000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-271000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-253000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-266000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-274000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-294000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-272000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-275000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-271000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-291000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-271000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-275000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-285000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,8 +7581,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,8 +7667,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,91 +7753,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-314000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-610000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-81000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>83000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-173000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>158000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-86000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-713000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-776000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-576000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-774000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-597000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-486000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-724000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>57000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-924000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7626,8 +7874,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7677,87 +7925,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-753000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1146000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-85000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-656000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1898000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-119000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-731000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-107000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1042000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-156000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-295000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-242000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>443000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>76000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-120000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>193000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-126000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>286000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>991000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,397 +656,409 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3041000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3087000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3092000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3182000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3329000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3221000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3268000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3290000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3517000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3641000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3661000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3738000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3800000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4390000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4612000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4676000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4847000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4887000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4924000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5029000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5125000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5167000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5192000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5228000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5306000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5350000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5375000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5427000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1700000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1624000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1687000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1706000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1692000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1653000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1652000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1737000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1850000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1740000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1817000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1826000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1999000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2058000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1985000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2086000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2151000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2115000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2136000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2231000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2236000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2232000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2235000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2257000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2334000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2243000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2300000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1387000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1468000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1495000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1623000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1529000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1615000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1638000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1780000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1921000</v>
       </c>
       <c r="N10" s="3">
         <v>1921000</v>
       </c>
       <c r="O10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="P10" s="3">
         <v>1974000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2391000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2554000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2691000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2761000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2736000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2809000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2893000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2894000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2931000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2960000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2993000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3049000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3016000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3132000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3127000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1078,8 +1090,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1180,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1256,56 +1272,59 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E14" s="3">
         <v>395000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>864000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>35000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>59000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-190000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-273000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2006000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>37000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8795000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-452000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3504000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-639000</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1316,23 +1335,23 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-8000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2665000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>79000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1340,13 +1359,16 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>6506000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1354,88 +1376,91 @@
         <v>674000</v>
       </c>
       <c r="E15" s="3">
+        <v>674000</v>
+      </c>
+      <c r="F15" s="3">
         <v>688000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>713000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>758000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>707000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>743000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>748000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>751000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>755000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>746000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>733000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>796000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>808000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>827000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>808000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>877000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>951000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1041000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1150000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1195000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1193000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1162000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1210000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1235000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1196000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1464,186 +1489,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3223000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3249000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3113000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3121000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3083000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3133000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3175000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3262000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3585000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3357000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3315000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3310000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6797000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2960000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3700000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3593000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3686000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3756000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3918000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4034000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6957000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4275000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4296000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4327000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4459000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4400000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4399000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10926000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-162000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>61000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>246000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>88000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>93000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-68000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>284000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>346000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>428000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1430000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>912000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1083000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1161000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1131000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1006000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>995000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>892000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>896000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>901000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>847000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>950000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>976000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1675,453 +1707,469 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-45000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-54000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-55000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-22000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-81000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-35000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-34000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-202000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>41000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-49000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-66000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>95000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-130000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-122000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>70000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-110000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-38000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>52000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>26000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>31000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>44000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E21" s="3">
         <v>557000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>721000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>829000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1026000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>876000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>871000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>810000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>885000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>998000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1141000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1227000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2108000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1617000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1961000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1928000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2044000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2099000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2171000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-617000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2082000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2089000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2042000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2046000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2141000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2216000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E22" s="3">
         <v>319000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>338000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>347000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>357000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>351000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>373000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>291000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>290000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>295000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>294000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>279000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>280000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>363000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>337000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>352000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>372000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>377000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>384000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>389000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>396000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>409000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>414000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>449000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>487000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>496000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>518000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>523000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-509000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-813000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1149000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-245000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-119000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-172000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>102000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-85000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>680000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>937000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>453000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>801000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>679000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>716000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>674000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>632000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>480000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>513000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>433000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>349000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>410000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>502000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-507000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-192000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-234000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-44000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-204000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-24000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>45000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-147000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>169000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-113000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>359000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>109000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>202000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>171000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>172000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>168000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>157000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>81000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>136000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>119000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>126000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>108000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>131000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>138000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2209,186 +2257,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-621000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-915000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-201000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>85000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-148000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>57000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-78000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>511000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>578000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>344000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>599000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>508000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>544000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>506000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>475000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>366000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>377000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>314000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>223000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>302000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>371000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-621000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-915000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-201000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>85000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-148000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-49000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>57000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-78000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>511000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>578000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>344000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>599000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>508000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>544000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>506000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>475000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>366000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>377000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>314000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>223000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>302000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>371000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2476,8 +2533,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2544,8 +2604,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2562,11 +2622,14 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2654,8 +2717,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2743,186 +2809,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E32" s="3">
         <v>45000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>54000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>55000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>22000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>81000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>35000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>34000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>202000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-41000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>49000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>66000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-95000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>130000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>122000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-70000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>110000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>38000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-52000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-26000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>19000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>11000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>44000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-621000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-915000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-201000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>85000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-148000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-49000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>57000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-78000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>511000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>578000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>344000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>599000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>508000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>544000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>506000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>475000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>366000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>377000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>314000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>223000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>302000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>371000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3010,191 +3085,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-621000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-915000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-201000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>85000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-148000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-49000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>57000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-78000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>511000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>578000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>344000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>599000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>508000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>544000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>506000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>475000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>366000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>377000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>314000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>223000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>302000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>371000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3226,8 +3310,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3259,97 +3344,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2401000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1568000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1900000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1889000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2640000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1495000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1580000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2234000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>311000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>411000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1148000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1251000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>252000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>360000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>366000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>354000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>635000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>935000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>486000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>406000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>526000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1763000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1564000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1404000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>410000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>441000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3437,364 +3526,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1721000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1692000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1580000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1730000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1254000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1351000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1369000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1610000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1553000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1581000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1450000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1528000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1552000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1529000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1586000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1723000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1605000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1970000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1953000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2035000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2184000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2284000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2281000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2346000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2590000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2474000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E44" s="3">
         <v>163000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>126000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>124000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>146000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>173000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>184000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>193000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>209000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>227000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>205000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>223000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>236000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>179000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>151000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>128000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>96000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>103000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>114000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>100000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>105000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>112000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>122000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>119000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>105000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>137000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>151000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>154000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4537000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4052000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3931000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>262000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>257000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>312000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>313000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>312000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>327000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2163000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2220000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2174000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2436000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7399000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9750000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9692000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9363000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9358000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>727000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>754000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>630000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>682000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>689000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>726000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>637000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>702000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>727000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>751000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7909000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8707000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7737000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4277000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4394000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4736000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3760000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3935000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4775000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4646000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4873000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5405000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5451000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9382000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11790000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11772000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11536000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11701000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3746000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3293000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3176000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3504000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4858000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4690000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4768000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4589000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>3820000</v>
       </c>
       <c r="AE46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3831,8 +3935,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3882,186 +3986,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20866000</v>
+      </c>
+      <c r="E48" s="3">
         <v>19107000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18665000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20568000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21540000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20344000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20089000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19908000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20988000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19606000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19432000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19321000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20506000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20713000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20720000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20829000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22346000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20926000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25993000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26091000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>28037000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>26290000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26079000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>27623000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>27765000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27595000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27704000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>27745000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4463000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4411000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4525000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6624000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6770000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6931000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7091000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7254000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7434000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9608000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9763000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18691000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18823000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22354000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22575000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22761000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22956000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23147000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>26530000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>26738000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>27089000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>30039000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>30372000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>30699000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>31101000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>31386000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>31734000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>32035000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4149,8 +4262,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4238,97 +4354,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>959000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2061000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2049000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2069000</v>
       </c>
-      <c r="G52" s="3">
-        <v>792000</v>
-      </c>
       <c r="H52" s="3">
+        <v>696000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1978000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2003000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2076000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>821000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1898000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1941000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1957000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>832000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2368000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2590000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2675000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1155000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2534000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2678000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2706000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1092000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2766000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2862000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1044000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1158000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1192000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4416,97 +4538,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34342000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34286000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32976000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33538000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33496000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33989000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32943000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33173000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>34018000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35921000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36168000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45530000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45612000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54817000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57675000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58037000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57993000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58308000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58947000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58828000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59394000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>62599000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64171000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64056000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>64742000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>64728000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>64508000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>64788000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4538,8 +4666,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4571,542 +4700,561 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1508000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1089000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>831000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>773000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>749000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>905000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>995000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1162000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1134000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1015000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1171000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1131000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1044000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1009000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1053000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>902000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>758000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>829000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>966000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1017000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1134000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1364000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1448000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1581000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1724000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1712000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1634000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>354000</v>
+      </c>
+      <c r="E58" s="3">
         <v>367000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>606000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>593000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>665000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>678000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>473000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>368000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>425000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>451000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>477000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>479000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>154000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>156000</v>
       </c>
       <c r="R58" s="3">
         <v>156000</v>
       </c>
       <c r="S58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="T58" s="3">
         <v>1554000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2501000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2595000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3841000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2427000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1487000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2885000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1129000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2300000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1744000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1595000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>632000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1525000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1583000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1456000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1379000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1312000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1421000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1446000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1598000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1111000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1582000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1534000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2560000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3699000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4232000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4572000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4597000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4857000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4970000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2949000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2929000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3073000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3028000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3139000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2993000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3234000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3133000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3266000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3260000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4390000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3932000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3632000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3545000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3639000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3940000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3738000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3816000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3534000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3920000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3963000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4848000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4897000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8715000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5781000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5655000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7169000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8300000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6510000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7787000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6634000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5879000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7472000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5703000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7258000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6589000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6495000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5373000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18466000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17578000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17565000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17334000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18453000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18142000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18411000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18591000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20871000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19740000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19899000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19743000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20418000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21764000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27965000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28397000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>27428000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27260000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28574000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>27599000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29410000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31105000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>31414000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33481000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32394000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>33381000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>33193000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34858000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1824000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3295000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3276000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3236000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2112000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2637000</v>
       </c>
       <c r="I62" s="3">
         <v>2637000</v>
       </c>
       <c r="J62" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2641000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1610000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2626000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2633000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2578000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9923000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11761000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11710000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11703000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11556000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11565000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12157000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12139000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12188000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11926000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11823000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11581000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11620000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11084000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11128000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11014000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5194,8 +5342,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5283,8 +5434,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5372,8 +5526,11 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5381,88 +5538,91 @@
         <v>35459000</v>
       </c>
       <c r="E66" s="3">
+        <v>35459000</v>
+      </c>
+      <c r="F66" s="3">
         <v>33571000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33249000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33032000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33647000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32477000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32669000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33601000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33702000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33884000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34535000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>35238000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42240000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45456000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45755000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>46153000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>47125000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>47241000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47525000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48232000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48910000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50709000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50765000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>51272000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>51054000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50816000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>51245000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5494,8 +5654,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5583,8 +5744,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5672,8 +5836,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5761,8 +5928,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5850,97 +6020,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-19701000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-19699000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19078000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-18163000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17962000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-18047000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6028,8 +6204,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6117,8 +6296,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6206,97 +6388,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1117000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1173000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-595000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>289000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>464000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>342000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>466000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>504000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>417000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2219000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2284000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10995000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10374000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12577000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12219000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12282000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11840000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11183000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11706000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11303000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11162000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13689000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13462000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13291000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13470000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13674000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13692000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13543000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6384,191 +6572,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-621000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-915000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-201000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>85000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-148000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-49000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>57000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-78000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>511000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>578000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>344000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>599000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>508000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>544000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>506000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>475000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>366000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>377000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>314000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>223000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>302000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>371000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6600,97 +6797,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>494000</v>
+      </c>
+      <c r="E83" s="3">
         <v>454000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>466000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>476000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>492000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>484000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>483000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>473000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>520000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>529000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>550000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>534000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>796000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>808000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>827000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>808000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>877000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>951000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1041000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1150000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1195000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1193000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1162000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1160000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1210000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1235000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1196000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1188000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6778,8 +6979,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6867,8 +7071,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6956,8 +7163,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7045,8 +7255,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7134,97 +7347,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2511000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>570000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1095000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>688000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2032000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>511000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1102000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>784000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>881000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>595000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>841000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1396000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1375000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1607000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1730000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1639000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1525000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1682000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1794000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1749000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1299000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1909000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1888000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1701000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7256,97 +7475,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1644000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1041000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-891000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-791000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-915000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-850000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-753000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-713000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-821000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-843000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-796000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-640000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-833000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-845000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-761000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-577000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-848000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-690000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-646000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-716000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-758000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-988000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-974000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-940000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-957000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-800000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7434,8 +7657,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7523,97 +7749,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1636000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1027000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-873000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-769000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-831000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-805000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-496000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-698000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1031000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-827000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-789000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-616000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4882000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1864000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-701000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-569000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-763000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-654000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-620000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-675000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-724000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-942000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-959000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7645,34 +7877,35 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>1000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>1000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
+      <c r="H96" s="3">
+        <v>3000</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>3000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>1000</v>
       </c>
       <c r="L96" s="3">
         <v>1000</v>
@@ -7681,61 +7914,64 @@
         <v>1000</v>
       </c>
       <c r="N96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O96" s="3">
         <v>8000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-255000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-254000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-271000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-253000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-266000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-274000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-294000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-272000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-275000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-271000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-291000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-275000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-285000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7823,8 +8059,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7912,8 +8151,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8001,97 +8243,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-324000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-651000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-314000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-610000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-81000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>83000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-173000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>158000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-86000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-713000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-776000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-576000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-774000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-597000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-486000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-724000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>57000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-924000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8128,8 +8376,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8179,93 +8427,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1398000</v>
+      </c>
+      <c r="E102" s="3">
         <v>833000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-333000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-753000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1146000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-85000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-656000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1898000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-119000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-731000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-107000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1042000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-156000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-295000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-242000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>443000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>76000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-120000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>193000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>286000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>991000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>98000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,409 +656,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2899000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3041000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3087000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3092000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3182000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3329000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3221000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3268000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3290000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3517000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3641000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3661000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3738000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3800000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4390000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4612000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4676000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4847000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4887000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4924000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5029000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5125000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5167000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5192000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5228000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5306000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5350000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5375000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5427000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1435000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1627000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1700000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1624000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1687000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1706000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1692000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1653000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1652000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1737000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1850000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1740000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1817000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1826000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1999000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2058000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1985000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2086000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2151000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2115000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2136000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2231000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2236000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2232000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2235000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2257000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2334000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2243000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2300000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1464000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1414000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1387000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1468000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1495000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1623000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1529000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1615000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1638000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1780000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1921000</v>
       </c>
       <c r="O10" s="3">
         <v>1921000</v>
       </c>
       <c r="P10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1974000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2391000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2554000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2691000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2761000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2736000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2809000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2893000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2894000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2931000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2960000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2993000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3049000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3016000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3132000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3127000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1091,8 +1103,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1183,8 +1196,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1275,59 +1291,62 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-370000</v>
+      </c>
+      <c r="E14" s="3">
         <v>138000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>395000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>864000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>35000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>59000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-190000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-273000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2006000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>37000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8795000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-452000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3504000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-639000</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1338,23 +1357,23 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-8000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2665000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>79000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1362,105 +1381,111 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>6506000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>674000</v>
+        <v>664000</v>
       </c>
       <c r="E15" s="3">
         <v>674000</v>
       </c>
       <c r="F15" s="3">
+        <v>674000</v>
+      </c>
+      <c r="G15" s="3">
         <v>688000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>713000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>758000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>707000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>743000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>748000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>751000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>755000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>746000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>733000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>796000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>808000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>827000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>808000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>877000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>951000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1041000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1150000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1195000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1193000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1162000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1210000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1235000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1196000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1490,192 +1515,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2919000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3223000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3249000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3113000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3121000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3083000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3133000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3175000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3262000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3585000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3357000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3315000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3310000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6797000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2960000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3700000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3593000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3686000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3756000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3918000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4034000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6957000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4275000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4296000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4327000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4459000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4400000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4399000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10926000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-182000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-162000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>61000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>246000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>88000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>93000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-68000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>284000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>346000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>428000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1430000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>912000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1083000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1161000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1131000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1006000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>995000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>892000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>896000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>901000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>847000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>950000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>976000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1708,468 +1740,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-75000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-45000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-54000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-55000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-22000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-81000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-35000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-34000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-202000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>41000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-49000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-66000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>95000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-130000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-122000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>70000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-110000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-38000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>52000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>26000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>31000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-44000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>44000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>682000</v>
+      </c>
+      <c r="E21" s="3">
         <v>567000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>557000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>721000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>829000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1026000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>876000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>871000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>810000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>885000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>998000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1141000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1227000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2108000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1617000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1961000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1928000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2044000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2099000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2171000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-617000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2082000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2089000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2042000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2046000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2141000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2216000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E22" s="3">
         <v>280000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>319000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>338000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>347000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>357000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>351000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>373000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>291000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>290000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>295000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>294000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>279000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>280000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>363000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>337000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>352000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>372000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>377000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>384000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>389000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>396000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>409000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>414000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>449000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>487000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>496000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>518000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>523000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-509000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-813000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1149000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-245000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-119000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-172000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>102000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-85000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>680000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>937000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>453000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>801000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>679000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>716000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>674000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>632000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>480000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>513000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>433000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>349000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>410000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>502000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-507000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-192000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-234000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-44000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-204000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-24000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>45000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-147000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>169000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-113000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>359000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>109000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>202000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>171000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>172000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>168000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>157000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>81000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>114000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>136000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>119000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>126000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>108000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>131000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>138000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2260,192 +2308,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-621000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-915000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-201000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>85000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-148000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>57000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-78000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>511000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>578000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>344000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>599000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>508000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>544000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>506000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>475000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>366000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>377000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>314000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>223000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>302000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>371000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-621000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-915000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-201000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>85000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-148000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-49000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>57000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-78000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>511000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>578000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>344000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>599000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>508000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>544000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>506000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>475000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>366000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>377000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>314000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>223000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>302000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>371000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2536,8 +2593,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2607,8 +2667,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2625,11 +2685,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2720,8 +2783,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2812,192 +2878,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E32" s="3">
         <v>75000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>45000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>54000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>55000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>22000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>81000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>35000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>34000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>202000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-41000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>49000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>66000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>130000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>122000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-70000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>110000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>38000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-52000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-26000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>19000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>44000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-621000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-915000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-201000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>85000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-148000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-49000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>57000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-78000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>511000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>578000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>344000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>599000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>508000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>544000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>506000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>475000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>366000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>377000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>314000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>223000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>302000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>371000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3088,197 +3163,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-621000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-915000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-201000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>85000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-148000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-49000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>57000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-78000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>511000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>578000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>344000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>599000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>508000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>544000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>506000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>475000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>366000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>377000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>314000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>223000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>302000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>371000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3311,8 +3395,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3345,100 +3430,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1625000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1003000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2401000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1568000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1900000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1889000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2640000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1495000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1580000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2234000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>311000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>411000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1148000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1251000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>252000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>360000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>366000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>354000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>635000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>935000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>486000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>406000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>526000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1763000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1564000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1404000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>410000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>441000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3529,376 +3618,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1629000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1800000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1721000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1692000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1580000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1730000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1254000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1351000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1369000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1610000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1553000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1581000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1450000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1528000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1552000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1529000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1586000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1723000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1605000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1970000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1953000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2035000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2184000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2284000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2281000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2346000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2590000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2474000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E44" s="3">
         <v>165000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>163000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>126000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>124000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>146000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>173000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>184000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>193000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>209000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>227000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>205000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>223000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>236000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>179000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>151000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>128000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>96000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>103000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>114000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>100000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>105000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>112000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>122000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>119000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>105000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>137000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>151000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>154000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4537000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4052000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3931000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>262000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>257000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>312000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>313000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>312000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>327000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2163000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2220000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2174000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2436000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7399000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9750000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9692000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9363000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9358000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>727000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>754000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>630000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>682000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>689000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>726000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>637000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>702000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>727000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>751000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4121000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7909000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8707000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7737000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4277000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4394000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4736000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3760000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3935000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4775000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4646000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4873000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5405000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5451000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9382000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11790000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11772000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11536000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11701000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3746000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3293000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3176000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3504000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4858000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4690000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4768000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4589000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>3820000</v>
       </c>
       <c r="AF46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3938,8 +4042,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3989,192 +4093,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19926000</v>
+      </c>
+      <c r="E48" s="3">
         <v>20866000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19107000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18665000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20568000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21540000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20344000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20089000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19908000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20988000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19606000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19432000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19321000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20506000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20713000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20720000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20829000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22346000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20926000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>25993000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26091000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28037000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26290000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26079000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>27623000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27765000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27595000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>27704000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27745000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4240000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4463000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4411000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4525000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6624000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6770000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6931000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7091000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7254000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7434000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9608000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9763000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18691000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18823000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>22354000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22575000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22761000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22956000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23147000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>26530000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>26738000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>27089000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>30039000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>30372000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>30699000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>31101000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>31386000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>31734000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>32035000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4265,8 +4378,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4357,100 +4473,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2335000</v>
+      </c>
+      <c r="E52" s="3">
         <v>959000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2061000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2049000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2069000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>696000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1978000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2003000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2076000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>821000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1898000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1941000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1957000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>832000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2368000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2590000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2675000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1155000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2534000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2678000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2706000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1092000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2766000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2862000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1044000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1158000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1192000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4541,100 +4663,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30622000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34342000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34286000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32976000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33538000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33496000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33989000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32943000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33173000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34018000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35921000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36168000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45530000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45612000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54817000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57675000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58037000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57993000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58308000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58947000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58828000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59394000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62599000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64171000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>64056000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>64742000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>64728000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>64508000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>64788000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4667,8 +4795,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4701,560 +4830,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1508000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1089000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>831000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>773000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>749000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>905000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>995000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1162000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1134000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1015000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1171000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1131000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1044000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1009000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1053000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>902000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>758000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>829000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>966000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1017000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1134000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1364000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1448000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1581000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1724000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1712000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1634000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E58" s="3">
         <v>354000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>367000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>606000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>593000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>665000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>678000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>473000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>368000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>425000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>451000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>477000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>479000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>154000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>156000</v>
       </c>
       <c r="S58" s="3">
         <v>156000</v>
       </c>
       <c r="T58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="U58" s="3">
         <v>1554000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2501000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2595000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3841000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2427000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1487000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2885000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1129000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2300000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1744000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1595000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>632000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1871000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1525000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1583000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1456000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1379000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1312000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1421000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1446000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1598000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1111000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1582000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1534000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2560000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3699000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4232000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4572000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4597000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4857000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4970000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2949000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2929000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3073000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3028000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3139000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2993000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3234000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3133000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3266000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3260000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4171000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4390000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3932000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3632000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3545000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3639000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3940000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3738000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3816000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3534000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3920000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3963000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4848000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4897000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8715000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5781000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5655000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7169000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8300000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6510000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7787000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6634000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5879000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7472000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5703000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7258000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6589000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6495000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5373000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12925000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18466000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17578000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17565000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17334000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18453000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18142000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18411000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18591000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20871000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19740000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19899000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19743000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20418000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21764000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27965000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28397000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27428000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>27260000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28574000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>27599000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29410000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>31105000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>31414000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33481000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>32394000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>33381000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>33193000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34858000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2982000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1824000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3295000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3276000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3236000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2112000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2637000</v>
       </c>
       <c r="J62" s="3">
         <v>2637000</v>
       </c>
       <c r="K62" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="L62" s="3">
         <v>2641000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1610000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2626000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2633000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2578000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9923000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11761000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11710000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11703000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11556000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11565000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12157000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12139000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12188000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11926000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11823000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11581000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11620000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11084000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11128000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11014000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5345,8 +5493,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5437,8 +5588,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5529,100 +5683,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>35459000</v>
+        <v>31939000</v>
       </c>
       <c r="E66" s="3">
         <v>35459000</v>
       </c>
       <c r="F66" s="3">
+        <v>35459000</v>
+      </c>
+      <c r="G66" s="3">
         <v>33571000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33249000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33032000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33647000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32477000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32669000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33601000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33702000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33884000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34535000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35238000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>42240000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45456000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45755000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46153000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>47125000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47241000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>47525000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48232000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48910000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50709000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50765000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>51272000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>51054000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>50816000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>51245000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5655,8 +5815,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5747,8 +5908,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5839,8 +6003,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5931,8 +6098,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6023,100 +6193,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-19901000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-19701000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19699000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-19078000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-18163000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17962000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-18047000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6207,8 +6383,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6299,8 +6478,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6391,100 +6573,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1317000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1117000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1173000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-595000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>289000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>464000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>342000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>466000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>504000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>417000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2219000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2284000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10995000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10374000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12577000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12219000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12282000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11840000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11183000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11706000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11303000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11162000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13689000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13462000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13291000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13470000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13674000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13692000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13543000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6575,197 +6763,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-621000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-915000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-201000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>85000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-148000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-49000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>57000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-78000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>511000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>578000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>344000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>599000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>508000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>544000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>506000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>475000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>366000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>377000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>314000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>223000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>302000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>371000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6798,100 +6995,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>461000</v>
+      </c>
+      <c r="E83" s="3">
         <v>494000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>454000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>466000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>476000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>492000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>484000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>483000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>473000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>520000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>529000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>550000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>534000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>796000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>808000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>827000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>808000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>877000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>951000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1041000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1150000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1195000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1193000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1162000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1210000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1235000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1196000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1188000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6982,8 +7183,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7074,8 +7278,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7166,8 +7373,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7258,8 +7468,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7350,100 +7563,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1323000</v>
+      </c>
+      <c r="E89" s="3">
         <v>562000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2511000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>570000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1095000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>688000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2032000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>511000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1102000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>784000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>881000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>595000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>841000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1123000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1396000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1375000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1607000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1730000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1639000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1525000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1682000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1794000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1749000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1299000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1909000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1888000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1701000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7476,100 +7695,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-943000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1644000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1041000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-891000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-791000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-915000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-850000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-753000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-713000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-821000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-843000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-796000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-640000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-833000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-845000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-761000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-577000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-848000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-690000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-646000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-716000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-758000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-988000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-974000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-940000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-957000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-800000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7660,8 +7883,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7752,100 +7978,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4050000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1636000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1027000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-873000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-769000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-831000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-805000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-496000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-698000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1031000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-827000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-789000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-616000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4882000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1864000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-701000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-569000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-763000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-654000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-620000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-675000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-724000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-942000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-959000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7878,37 +8110,38 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>1000</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>3000</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>3000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>1000</v>
       </c>
       <c r="M96" s="3">
         <v>1000</v>
@@ -7917,61 +8150,64 @@
         <v>1000</v>
       </c>
       <c r="O96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P96" s="3">
         <v>8000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-255000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-254000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-271000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-253000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-266000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-274000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-294000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-272000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-275000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-291000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-275000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-285000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8062,8 +8298,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8154,8 +8393,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8246,100 +8488,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4751000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-324000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-651000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-314000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-610000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-81000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>83000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-173000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>158000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-86000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-713000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-776000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-576000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-774000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-597000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-486000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-724000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>57000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-924000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8379,8 +8627,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8430,96 +8678,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>622000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1398000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>833000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-333000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-753000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1146000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-85000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-656000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1898000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-119000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-731000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-107000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1042000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-156000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-295000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-242000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>443000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>76000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>193000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>286000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>991000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-44000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>98000</v>
       </c>
     </row>
